--- a/data/Mau_De_KTTX_Tin12_Bai4.xlsx
+++ b/data/Mau_De_KTTX_Tin12_Bai4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF22CA1B-4976-4C6C-89C1-FEE4B5B06719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72405EA8-E12B-4E8B-A573-308A7BFBBBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="CauHoi" sheetId="2" r:id="rId2"/>
     <sheet name="HuongDan" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="537">
   <si>
     <t>Lớp</t>
   </si>
@@ -69,223 +69,1036 @@
     <t>Đáp án đúng</t>
   </si>
   <si>
+    <t>Mã đề</t>
+  </si>
+  <si>
     <t>MC</t>
   </si>
   <si>
-    <t>Giao thức mạng (network protocol) là gì?</t>
-  </si>
-  <si>
-    <t>Tập hợp các thiết bị phần cứng trong mạng</t>
-  </si>
-  <si>
-    <t>Tập hợp các quy định về cách thức giao tiếp để truyền dữ liệu giữa các đối tượng tham gia mạng</t>
-  </si>
-  <si>
-    <t>Phần mềm dùng để quản lý tài khoản người dùng</t>
-  </si>
-  <si>
-    <t>Địa chỉ vật lý của thiết bị mạng</t>
+    <t>Giao thức mạng là gì?</t>
+  </si>
+  <si>
+    <t>Tập hợp các quy định về cách giao tiếp giữa các đối tượng tham gia truyền nhận dữ liệu qua mạng.</t>
+  </si>
+  <si>
+    <t>Một địa chỉ bằng số gắn cố định với phần cứng.</t>
+  </si>
+  <si>
+    <t>Một thiết bị dùng để chuyển tiếp dữ liệu.</t>
+  </si>
+  <si>
+    <t>Một phần mềm dùng để soạn thư.</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Giao thức nào quy định việc gửi thư điện tử theo bài học?</t>
+  </si>
+  <si>
+    <t>POP3</t>
+  </si>
+  <si>
+    <t>SMTP</t>
+  </si>
+  <si>
+    <t>IMAP</t>
+  </si>
+  <si>
+    <t>DNS</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Giao thức TCP/IP gồm hai giao thức cốt lõi nào?</t>
-  </si>
-  <si>
-    <t>HTTP và FTP</t>
-  </si>
-  <si>
-    <t>SMTP và POP3</t>
-  </si>
-  <si>
-    <t>TCP và IP</t>
-  </si>
-  <si>
-    <t>DNS và DHCP</t>
+    <t>IPv4 trong bài được mô tả có độ dài bao nhiêu byte?</t>
+  </si>
+  <si>
+    <t>2 byte</t>
+  </si>
+  <si>
+    <t>4 byte</t>
+  </si>
+  <si>
+    <t>6 byte</t>
+  </si>
+  <si>
+    <t>8 byte</t>
+  </si>
+  <si>
+    <t>Trong ví dụ thư điện tử, POP3 hoặc IMAP được dùng cho hoạt động nào?</t>
+  </si>
+  <si>
+    <t>Gửi thư từ người gửi tới máy chủ thư.</t>
+  </si>
+  <si>
+    <t>Lấy thư về từ hộp thư của người nhận.</t>
+  </si>
+  <si>
+    <t>Định tuyến gói tin giữa các LAN.</t>
+  </si>
+  <si>
+    <t>Kiểm tra lỗi truyền Ethernet.</t>
+  </si>
+  <si>
+    <t>Vì sao Ethernet cần mã kiểm tra đi kèm dữ liệu?</t>
+  </si>
+  <si>
+    <t>Để phát hiện lỗi truyền và có thể yêu cầu gửi lại.</t>
+  </si>
+  <si>
+    <t>Để đổi địa chỉ IP thành tên miền.</t>
+  </si>
+  <si>
+    <t>Để cấp số hiệu cổng cho ứng dụng.</t>
+  </si>
+  <si>
+    <t>Để chọn đường đi trên Internet.</t>
+  </si>
+  <si>
+    <t>Vì sao TCP đánh số các gói dữ liệu theo từng ứng dụng?</t>
+  </si>
+  <si>
+    <t>Để các gói đến nơi nhận có thể được ráp lại đúng thứ tự theo từng ứng dụng.</t>
+  </si>
+  <si>
+    <t>Để thay địa chỉ MAC bằng địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>Để router tạo bảng định tuyến.</t>
+  </si>
+  <si>
+    <t>Để biến tên miền thành địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>Một máy A gửi dữ liệu tới máy B ở LAN khác. Theo bài học, quá trình phù hợp nhất là:</t>
+  </si>
+  <si>
+    <t>A gửi trực tiếp bằng MAC của B trên toàn Internet.</t>
+  </si>
+  <si>
+    <t>Dữ liệu được gửi dựa trên IP, router chuyển tiếp tới LAN của B, sau đó MAC được dùng để tới B.</t>
+  </si>
+  <si>
+    <t>A chỉ cần biết tên miền của B và không cần router.</t>
+  </si>
+  <si>
+    <t>A gửi dữ liệu qua DNS rồi DNS chuyển gói tin tới B.</t>
+  </si>
+  <si>
+    <t>Một router có bảng: nhóm X → cổng 1; nhóm Y → cổng 2; cổng mặc định → cổng 3. Gói có địa chỉ đích thuộc nhóm Y. Router nên:</t>
+  </si>
+  <si>
+    <t>Gửi theo cổng 1.</t>
+  </si>
+  <si>
+    <t>Gửi theo cổng 2.</t>
+  </si>
+  <si>
+    <t>Gửi theo cổng 3.</t>
+  </si>
+  <si>
+    <t>Gửi đồng thời cả 3 cổng.</t>
+  </si>
+  <si>
+    <t>Một ứng dụng gửi nhiều gói qua các router khác nhau nên gói sau có thể đến trước gói trước. Cơ chế nào trong bài giúp xử lí tình huống này?</t>
+  </si>
+  <si>
+    <t>DNS đổi tên gói tin.</t>
+  </si>
+  <si>
+    <t>TCP đánh số gói để ráp lại đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>Ethernet thay đổi địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>ICMP tự động sắp xếp dữ liệu ứng dụng.</t>
+  </si>
+  <si>
+    <t>Một trường có hai máy trong cùng LAN. Máy A gửi dữ liệu cho máy B. Sau đó trường kết nối LAN này với LAN khác và gửi dữ liệu tới máy C ở LAN kia. Điểm khác biệt cốt lõi là:</t>
+  </si>
+  <si>
+    <t>Cả hai trường hợp đều chỉ dùng MAC từ đầu đến cuối.</t>
+  </si>
+  <si>
+    <t>Trường hợp cùng LAN chỉ cần MAC; trường hợp khác LAN cần IP và router, rồi MAC được dùng trong LAN đích.</t>
+  </si>
+  <si>
+    <t>Cùng LAN phải dùng DNS, khác LAN chỉ dùng Ethernet.</t>
+  </si>
+  <si>
+    <t>Cùng LAN dùng TCP, khác LAN không cần giao thức.</t>
+  </si>
+  <si>
+    <t>Một gói tin đến router nhưng địa chỉ đích không có mục tương ứng trong bảng định tuyến tĩnh. Nếu router có cổng mặc định, cách xử lí phù hợp là:</t>
+  </si>
+  <si>
+    <t>Hủy gói vì không có mục cụ thể.</t>
+  </si>
+  <si>
+    <t>Gửi theo cổng mặc định.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ IP đích thành địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Chuyển gói sang DNS để tìm đường.</t>
+  </si>
+  <si>
+    <t>Một người dùng biết địa chỉ IP máy chủ nhưng khó nhớ dãy số. Họ muốn sử dụng một tên bằng chữ thay thế địa chỉ IP. Giao thức phù hợp theo bài là:</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>Ethernet</t>
+  </si>
+  <si>
+    <t>ICMP</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>Xét tình huống gửi dữ liệu qua Internet:</t>
+  </si>
+  <si>
+    <t>a) Giao thức mạng quy định cách thức giao tiếp giữa các đối tượng truyền nhận dữ liệu.</t>
+  </si>
+  <si>
+    <t>b) Khi hai máy không cùng LAN, router hỗ trợ chuyển tiếp dữ liệu dựa trên IP.</t>
+  </si>
+  <si>
+    <t>c) Nếu gói đến không có mục trong bảng định tuyến tĩnh nhưng có cổng mặc định, router có thể chuyển theo cổng mặc định.</t>
+  </si>
+  <si>
+    <t>d) Nếu máy nhận ở LAN khác, máy gửi có thể bỏ qua router vì chỉ cần biết MAC của máy nhận từ đầu.</t>
+  </si>
+  <si>
+    <t>ĐĐĐS</t>
+  </si>
+  <si>
+    <t>Xét việc truyền dữ liệu bằng TCP:</t>
+  </si>
+  <si>
+    <t>a) TCP có cấp số hiệu cổng ứng dụng.</t>
+  </si>
+  <si>
+    <t>b) TCP đánh số gói để ở nơi nhận có thể ráp lại đúng thứ tự theo từng ứng dụng.</t>
+  </si>
+  <si>
+    <t>c) Nếu gói thứ 2 đến trước gói thứ 1, cơ chế đánh số của TCP giúp nhận biết thứ tự để ráp lại.</t>
+  </si>
+  <si>
+    <t>d) Vì TCP có đánh số gói nên dữ liệu luôn đi qua cùng một router và chắc chắn không thể có gói đến khác thứ tự.</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ IP nhị phân 11000000 10101000 00000001 00000011 sang dạng thập phân.</t>
+  </si>
+  <si>
+    <t>192.168.1.3</t>
+  </si>
+  <si>
+    <t>Một máy gửi dữ liệu đến máy ở LAN khác. Hãy nêu chuỗi xử lí chính theo bài học, từ khi dữ liệu rời máy gửi đến khi được chuyển tới máy nhận.</t>
+  </si>
+  <si>
+    <t>Dựa trên IP để router chuyển tiếp tới LAN đích; khi đến LAN đích, dùng MAC để chuyển tới máy nhận.|IP router LAN đích MAC</t>
+  </si>
+  <si>
+    <t>Giao thức truyền tin trong mạng cục bộ được nêu trong bài là:</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Địa chỉ gắn với phần cứng, được mô tả dài 6 byte là:</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>Tên miền</t>
+  </si>
+  <si>
+    <t>Cổng ứng dụng</t>
+  </si>
+  <si>
+    <t>Giao thức kiểm soát việc truyền dữ liệu có tên viết tắt là:</t>
+  </si>
+  <si>
+    <t>Tại sao truyền dữ liệu Ethernet theo từng gói có độ dài xác định?</t>
+  </si>
+  <si>
+    <t>Để tránh một lượng tin dài không giới hạn làm quá tải máy nhận và cản trở các cuộc truyền khác.</t>
+  </si>
+  <si>
+    <t>Để thay thế địa chỉ MAC bằng tên miền.</t>
+  </si>
+  <si>
+    <t>Để router không cần bảng định tuyến.</t>
+  </si>
+  <si>
+    <t>Để mọi dữ liệu chỉ đi qua một đường truyền.</t>
+  </si>
+  <si>
+    <t>Theo bài, tại sao TCP cần cơ chế xác nhận?</t>
+  </si>
+  <si>
+    <t>Để nơi gửi biết gói tin có sai sót hoặc thất lạc và yêu cầu gửi lại khi cần.</t>
+  </si>
+  <si>
+    <t>Để xác định tên miền cấp cao nhất.</t>
+  </si>
+  <si>
+    <t>Để tạo địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Để quy định cách mã hóa trang web.</t>
+  </si>
+  <si>
+    <t>Vì sao nhiều cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí khi dữ liệu được tách thành gói?</t>
+  </si>
+  <si>
+    <t>Vì từng gói của các cuộc truyền có thể được truyền xen kẽ, giúp tận dụng đường truyền.</t>
+  </si>
+  <si>
+    <t>Vì mỗi cuộc truyền được cấp một đường vật lí riêng.</t>
+  </si>
+  <si>
+    <t>Vì router không cần chọn cổng.</t>
+  </si>
+  <si>
+    <t>Vì DNS chia đường truyền thành các tên miền.</t>
+  </si>
+  <si>
+    <t>Một máy có IP 192.168.1.3. Dạng nhị phân tương ứng là:</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000001 00000011</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000011 00000001</t>
+  </si>
+  <si>
+    <t>11000000 10101001 00000001 00000011</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000010 00000011</t>
+  </si>
+  <si>
+    <t>Một thiết bị nhận dữ liệu trong LAN nhưng địa chỉ MAC đích của khung không trùng với MAC của thiết bị đó. Theo mô tả trong bài, thiết bị đó:</t>
+  </si>
+  <si>
+    <t>Nhận khung vì IP trùng.</t>
+  </si>
+  <si>
+    <t>Không nhận khung đó vì trong LAN máy tính nhận các gói có MAC đích trùng MAC của mình.</t>
+  </si>
+  <si>
+    <t>Luôn chuyển khung cho DNS.</t>
+  </si>
+  <si>
+    <t>Đổi MAC thành IP rồi nhận.</t>
+  </si>
+  <si>
+    <t>Khi ping một thiết bị, theo bài công cụ ping gửi loại yêu cầu nào?</t>
+  </si>
+  <si>
+    <t>HTTP Request</t>
+  </si>
+  <si>
+    <t>SMTP Request</t>
+  </si>
+  <si>
+    <t>ICMP Echo Request</t>
+  </si>
+  <si>
+    <t>DNS Request</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>Giao thức IP có chức năng chính nào dưới đây?</t>
-  </si>
-  <si>
-    <t>Chia dữ liệu thành các gói nhỏ và đảm bảo thứ tự khi nhận</t>
-  </si>
-  <si>
-    <t>Thiết lập địa chỉ cho các thiết bị và dẫn đường các gói dữ liệu từ máy gửi đến máy nhận</t>
-  </si>
-  <si>
-    <t>Xác nhận việc gửi lại dữ liệu khi bị mất</t>
-  </si>
-  <si>
-    <t>Quản lý cổng ứng dụng trên máy tính</t>
-  </si>
-  <si>
-    <t>Hiện nay có bao nhiêu phiên bản địa chỉ IP chính được sử dụng?</t>
-  </si>
-  <si>
-    <t>1 (chỉ IPv4)</t>
-  </si>
-  <si>
-    <t>2 (IPv4 và IPv6)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Địa chỉ MAC khác địa chỉ IP ở điểm nào?</t>
-  </si>
-  <si>
-    <t>MAC là địa chỉ logic, IP là địa chỉ vật lý</t>
-  </si>
-  <si>
-    <t>MAC là địa chỉ vật lý cố định của card mạng, IP là địa chỉ logic có thể thay đổi</t>
-  </si>
-  <si>
-    <t>Cả hai đều là địa chỉ vật lý</t>
-  </si>
-  <si>
-    <t>MAC chỉ dùng trong mạng LAN, IP chỉ dùng trên Internet</t>
-  </si>
-  <si>
-    <t>TF</t>
-  </si>
-  <si>
-    <t>Xét các phát biểu về giao thức IP. Chọn Đúng hoặc Sai cho từng ý:</t>
-  </si>
-  <si>
-    <t>a) Giao thức IP quy định cách thiết lập địa chỉ và dẫn đường các gói dữ liệu.</t>
-  </si>
-  <si>
-    <t>b) IPv4 sử dụng 128 bit để biểu diễn địa chỉ.</t>
-  </si>
-  <si>
-    <t>c) Địa chỉ IP và địa chỉ MAC là hoàn toàn giống nhau.</t>
-  </si>
-  <si>
-    <t>d) Router đóng vai trò chuyển tiếp các gói tin theo địa chỉ IP.</t>
-  </si>
-  <si>
-    <t>ĐSSD</t>
-  </si>
-  <si>
-    <t>Xét các phát biểu về giao thức TCP. Chọn Đúng hoặc Sai:</t>
-  </si>
-  <si>
-    <t>a) TCP đảm bảo dữ liệu được truyền đến đúng ứng dụng và theo đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>b) Giao thức IP đã đủ để đảm bảo truyền dữ liệu tin cậy đến ứng dụng cụ thể.</t>
-  </si>
-  <si>
-    <t>c) TCP chia dữ liệu thành các gói nhỏ trước khi truyền.</t>
-  </si>
-  <si>
-    <t>d) TCP cung cấp cơ chế xác nhận và gửi lại dữ liệu khi cần.</t>
-  </si>
-  <si>
-    <t>ĐSĐĐ</t>
-  </si>
-  <si>
-    <t>Xét các phát biểu về địa chỉ mạng. Chọn Đúng/Sai:</t>
-  </si>
-  <si>
-    <t>a) Mỗi thiết bị tham gia Internet đều phải có địa chỉ IP.</t>
-  </si>
-  <si>
-    <t>b) Địa chỉ MAC thay đổi mỗi khi máy tính kết nối mạng khác.</t>
-  </si>
-  <si>
-    <t>c) IPv6 ra đời để giải quyết tình trạng cạn kiệt địa chỉ IPv4.</t>
-  </si>
-  <si>
-    <t>d) Router hoạt động ở tầng mạng và định tuyến theo địa chỉ IP.</t>
-  </si>
-  <si>
-    <t>Xét các phát biểu về Internet và TCP/IP. Chọn Đúng/Sai:</t>
-  </si>
-  <si>
-    <t>a) Internet hoạt động theo bộ giao thức TCP/IP.</t>
-  </si>
-  <si>
-    <t>b) HTTP là một trong hai giao thức cốt lõi của TCP/IP.</t>
-  </si>
-  <si>
-    <t>c) Cổng (port) giúp phân biệt các ứng dụng khác nhau trên cùng một máy.</t>
-  </si>
-  <si>
-    <t>d) SMTP dùng để gửi thư điện tử.</t>
-  </si>
-  <si>
-    <t>Xét các phát biểu về truyền dữ liệu. Chọn Đúng/Sai:</t>
-  </si>
-  <si>
-    <t>a) Giao thức mạng ra đời nhằm xác định cách định dạng, truyền, nhận dữ liệu.</t>
-  </si>
-  <si>
-    <t>b) IP đảm bảo dữ liệu đến đúng ứng dụng cụ thể trên máy nhận.</t>
-  </si>
-  <si>
-    <t>c) TCP sử dụng số thứ tự gói tin để sắp xếp lại đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>d) Khi gói tin bị mất, TCP có thể yêu cầu gửi lại.</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>Viết tên đầy đủ bằng tiếng Anh của giao thức TCP (chỉ cần viết tên).</t>
+    <t>Một học sinh nhập ping www.google.com. Theo bài, tên miền trong lệnh ping có thể được dùng thay cho địa chỉ IP nhờ cơ chế của:</t>
+  </si>
+  <si>
+    <t>Một router có nhiều cổng WAN. Gói tin đến có địa chỉ thuộc nhóm được chỉ dẫn đi qua cổng 4. Router nên xử lí thế nào?</t>
+  </si>
+  <si>
+    <t>Chọn cổng 4 để gửi tiếp.</t>
+  </si>
+  <si>
+    <t>Chỉ dùng cổng mặc định dù đã có chỉ dẫn.</t>
+  </si>
+  <si>
+    <t>Gửi qua mọi cổng WAN.</t>
+  </si>
+  <si>
+    <t>Đổi IP thành MAC rồi dừng chuyển tiếp.</t>
+  </si>
+  <si>
+    <t>Hai gói dữ liệu của cùng một ứng dụng đi theo các đường khác nhau và gói B đến trước gói A. Theo bài, xử lí nào phù hợp nhất?</t>
+  </si>
+  <si>
+    <t>TCP dùng số thứ tự để ráp dữ liệu về đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>DNS đổi thứ tự hai gói.</t>
+  </si>
+  <si>
+    <t>Ethernet yêu cầu router gửi lại mọi gói.</t>
+  </si>
+  <si>
+    <t>ICMP tự động ráp dữ liệu ứng dụng.</t>
+  </si>
+  <si>
+    <t>Xét địa chỉ và truyền dữ liệu trong LAN:</t>
+  </si>
+  <si>
+    <t>a) IPv4 được viết theo kiểu dot decimal, các byte ở dạng thập phân và cách nhau bằng dấu chấm.</t>
+  </si>
+  <si>
+    <t>b) MAC được mô tả là địa chỉ 6 byte gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>c) Nếu hai máy cùng LAN, theo bài chỉ cần địa chỉ MAC để máy nhận xác định các gói dành cho mình.</t>
+  </si>
+  <si>
+    <t>d) Nếu hai máy khác LAN, địa chỉ MAC của máy nhận ngoài LAN phải được máy gửi xác định trực tiếp từ đầu thì router mới chuyển được.</t>
+  </si>
+  <si>
+    <t>Xét DNS và ICMP:</t>
+  </si>
+  <si>
+    <t>a) DNS cho phép dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
+  </si>
+  <si>
+    <t>b) Ping dùng ICMP để kiểm tra kết nối giữa các thiết bị.</t>
+  </si>
+  <si>
+    <t>c) Khi người dùng gõ tên miền trong lệnh ping, tên miền có thể thay cho địa chỉ IP theo chức năng DNS được nêu trong bài.</t>
+  </si>
+  <si>
+    <t>d) Vì ping dùng ICMP nên ping có chức năng thay thế TCP trong việc đảm bảo dữ liệu ứng dụng đến đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ IP 131.214.23.16 sang dạng nhị phân.</t>
+  </si>
+  <si>
+    <t>10000011 11010110 00010111 00010000|10000011110101100001011100010000</t>
+  </si>
+  <si>
+    <t>Một người dùng muốn truy cập tài nguyên bằng tên “moet.edu.vn” thay vì nhớ địa chỉ IP. Giải thích giao thức nào hỗ trợ cách sử dụng này và lợi ích chính là gì.</t>
+  </si>
+  <si>
+    <t>DNS; giúp dùng tên bằng chữ dễ nhớ thay cho địa chỉ IP khó nhớ.|DNS</t>
+  </si>
+  <si>
+    <t>Giao thức được nêu để quy định cách biểu diễn (mã hóa) các trang web là:</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Giao thức cho phép người nhận lấy thư điện tử là:</t>
+  </si>
+  <si>
+    <t>POP3 hoặc IMAP</t>
+  </si>
+  <si>
+    <t>Địa chỉ IP trong bài (IPv4) thường được viết bằng:</t>
+  </si>
+  <si>
+    <t>4 byte ở dạng nhị phân không có dấu phân cách</t>
+  </si>
+  <si>
+    <t>4 byte, mỗi byte viết thập phân và ngăn cách bằng dấu chấm</t>
+  </si>
+  <si>
+    <t>6 byte thập phân</t>
+  </si>
+  <si>
+    <t>8 byte thập phân</t>
+  </si>
+  <si>
+    <t>Vì sao địa chỉ IP có thể khác MAC về tính chất?</t>
+  </si>
+  <si>
+    <t>IP được gán cho thiết bị và có thể thay đổi; MAC gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>IP và MAC luôn giống nhau.</t>
+  </si>
+  <si>
+    <t>IP chỉ dùng trong LAN.</t>
+  </si>
+  <si>
+    <t>MAC dùng để định tuyến Internet.</t>
+  </si>
+  <si>
+    <t>TCP giúp đảm bảo điều gì khi truyền dữ liệu?</t>
+  </si>
+  <si>
+    <t>Dữ liệu đến an toàn, có thể gửi lại khi mất, đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>Chỉ gán địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>Chỉ phân giải tên miền.</t>
+  </si>
+  <si>
+    <t>Chỉ tạo khung Ethernet.</t>
+  </si>
+  <si>
+    <t>DNS có lợi ích chính nào?</t>
+  </si>
+  <si>
+    <t>Dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
+  </si>
+  <si>
+    <t>Thay thế router.</t>
+  </si>
+  <si>
+    <t>Tăng độ dài MAC.</t>
+  </si>
+  <si>
+    <t>Mã hóa SMTP.</t>
+  </si>
+  <si>
+    <t>Đổi 00001010 00011001 00000000 11111111 sang thập phân chọn phương án đúng nhất (câu liên quan vận dụng):</t>
+  </si>
+  <si>
+    <t>10.25.0.255</t>
+  </si>
+  <si>
+    <t>10.25.0.254</t>
+  </si>
+  <si>
+    <t>11.25.0.255</t>
+  </si>
+  <si>
+    <t>10.24.0.255</t>
+  </si>
+  <si>
+    <t>Khi hai máy khác LAN, dữ liệu cần:</t>
+  </si>
+  <si>
+    <t>IP và router chuyển tiếp, rồi MAC trong LAN đích.</t>
+  </si>
+  <si>
+    <t>Chỉ MAC từ đầu đến cuối.</t>
+  </si>
+  <si>
+    <t>Chỉ DNS.</t>
+  </si>
+  <si>
+    <t>Chỉ SMTP.</t>
+  </si>
+  <si>
+    <t>Cơ chế TCP xử lý gói đến lệch thứ tự là:</t>
+  </si>
+  <si>
+    <t>Đánh số gói để ráp lại đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>DNS đổi thứ tự.</t>
+  </si>
+  <si>
+    <t>Ethernet đảo gói.</t>
+  </si>
+  <si>
+    <t>ICMP ráp ứng dụng.</t>
+  </si>
+  <si>
+    <t>Ping gửi loại yêu cầu nào?</t>
+  </si>
+  <si>
+    <t>Router có cổng mặc định khi không có mục đích trong bảng sẽ:</t>
+  </si>
+  <si>
+    <t>Hủy gói.</t>
+  </si>
+  <si>
+    <t>Đổi thành MAC.</t>
+  </si>
+  <si>
+    <t>Gửi DNS.</t>
+  </si>
+  <si>
+    <t>TCP/IP là:</t>
+  </si>
+  <si>
+    <t>Bộ giao thức nền tảng của Internet.</t>
+  </si>
+  <si>
+    <t>Chỉ dùng trong LAN.</t>
+  </si>
+  <si>
+    <t>Chỉ email.</t>
+  </si>
+  <si>
+    <t>Chỉ Ethernet.</t>
+  </si>
+  <si>
+    <t>Xét IP, MAC và LAN:</t>
+  </si>
+  <si>
+    <t>a) IPv4 thường viết 4 byte dạng thập phân cách nhau bằng dấu chấm.</t>
+  </si>
+  <si>
+    <t>b) MAC là địa chỉ gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>c) Cùng LAN có thể dùng MAC để nhận đúng máy đích.</t>
+  </si>
+  <si>
+    <t>d) Khác LAN thì máy gửi luôn biết sẵn MAC máy nhận từ đầu mà không cần router.</t>
+  </si>
+  <si>
+    <t>Xét TCP:</t>
+  </si>
+  <si>
+    <t>a) TCP kiểm soát truyền dữ liệu.</t>
+  </si>
+  <si>
+    <t>b) TCP có thể yêu cầu gửi lại khi mất gói.</t>
+  </si>
+  <si>
+    <t>c) Đánh số gói giúp ráp đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>d) TCP bảo đảm mọi gói luôn đi cùng một đường và không bao giờ lệch thứ tự.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ 00001010 00011001 00000000 11111111 sang dạng thập phân.</t>
+  </si>
+  <si>
+    <t>Trong một phiên truyền, các gói dữ liệu đến router có thể đi các đường khác nhau và đến nơi nhận không đúng thứ tự. Hãy nêu hai cơ chế TCP trong bài giúp dữ liệu được truyền tin cậy.</t>
+  </si>
+  <si>
+    <t>Đánh số gói để ráp đúng thứ tự; cơ chế xác nhận để phát hiện sai sót/thất lạc và yêu cầu gửi lại khi cần.|đánh số|xác nhận</t>
+  </si>
+  <si>
+    <t>Giao thức nào được nêu là giao thức định tuyến/chọn đường?</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Tên đầy đủ của TCP trong bài là:</t>
   </si>
   <si>
     <t>Transmission Control Protocol</t>
   </si>
   <si>
-    <t>Viết tên đầy đủ bằng tiếng Anh của giao thức IP.</t>
-  </si>
-  <si>
-    <t>Internet Protocol</t>
-  </si>
-  <si>
-    <t>Một địa chỉ IPv4 ở dạng nhị phân là 11000000.10101000.00000001.00000001. Hãy viết địa chỉ này ở dạng thập phân (x.x.x.x).</t>
-  </si>
-  <si>
-    <t>192.168.1.1</t>
-  </si>
-  <si>
-    <t>Giao thức nào được dùng để gửi thư điện tử? (viết tên viết tắt)</t>
-  </si>
-  <si>
-    <t>SMTP</t>
-  </si>
-  <si>
-    <t>IPv4 sử dụng bao nhiêu bit để biểu diễn địa chỉ? (chỉ viết số)</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>HƯỚNG DẪN SỬ DỤNG FILE NÀY VỚI TRANG THI WEBH2T</t>
-  </si>
-  <si>
-    <t>1. Sheet HocSinh: cột Lớp + Họ và tên. Cột Điểm để trống (hệ thống sẽ ghi sau khi học sinh nộp bài nếu dùng cloud).</t>
-  </si>
-  <si>
-    <t>2. Sheet CauHoi: Phần 1=MC (12 câu khuyến nghị), Phần 2=TF (2 câu), Phần 3=SA (2 câu). File mẫu có 5 câu/phần để minh họa.</t>
-  </si>
-  <si>
-    <t>3. Đáp án MC: A/B/C/D. Đáp án TF: 4 ký tự Đ hoặc S (ví dụ ĐSSD). Đáp án SA: text, nhiều đáp án cách bằng |</t>
-  </si>
-  <si>
-    <t>4. Đưa file này lên thư mục data/ của repo webh2t.github.io (hoặc bất kỳ URL công khai).</t>
-  </si>
-  <si>
-    <t>5. Trong trang thi, GVCN dán link raw của file hoặc để hệ thống tự load từ đường dẫn mặc định.</t>
+    <t>Transfer Control Port</t>
+  </si>
+  <si>
+    <t>Transport Connection Protocol</t>
+  </si>
+  <si>
+    <t>Transmission Channel Protocol</t>
+  </si>
+  <si>
+    <t>ICMP được nêu là giao thức cho phép:</t>
+  </si>
+  <si>
+    <t>gửi yêu cầu đến máy tính/thiết bị mạng/ứng dụng để lấy thông tin phản hồi</t>
+  </si>
+  <si>
+    <t>soạn và gửi thư điện tử</t>
+  </si>
+  <si>
+    <t>đổi tên miền thành MAC</t>
+  </si>
+  <si>
+    <t>quy định khung Ethernet</t>
+  </si>
+  <si>
+    <t>Vì sao khi hai máy khác LAN dữ liệu không thể truyền trực tiếp như trong cùng LAN?</t>
+  </si>
+  <si>
+    <t>Máy gửi không thể xác định trực tiếp MAC của máy nhận ngoài LAN và cần router hỗ trợ chuyển tiếp.</t>
+  </si>
+  <si>
+    <t>Vì không có DNS.</t>
+  </si>
+  <si>
+    <t>Vì TCP không hoạt động ngoài LAN.</t>
+  </si>
+  <si>
+    <t>Vì Ethernet không tồn tại trong LAN.</t>
+  </si>
+  <si>
+    <t>Tại sao TCP cần gắn nhãn cổng ứng dụng vào gói dữ liệu?</t>
+  </si>
+  <si>
+    <t>Để dữ liệu không bị lẫn giữa các ứng dụng.</t>
+  </si>
+  <si>
+    <t>Để xác định MAC của router.</t>
+  </si>
+  <si>
+    <t>Để đổi IP thành tên miền.</t>
+  </si>
+  <si>
+    <t>Để xác định địa chỉ đường truyền vật lí.</t>
+  </si>
+  <si>
+    <t>DNS giúp ích gì khi sử dụng Internet?</t>
+  </si>
+  <si>
+    <t>Cho phép dùng tên bằng chữ thay cho địa chỉ IP vốn khó nhớ.</t>
+  </si>
+  <si>
+    <t>Tạo mã kiểm tra Ethernet.</t>
+  </si>
+  <si>
+    <t>Đảm bảo TCP gửi lại mọi gói.</t>
+  </si>
+  <si>
+    <t>Chọn cổng WAN cho router.</t>
+  </si>
+  <si>
+    <t>Một địa chỉ IPv4 có dạng 192.168.13.210. Byte thứ tư ở dạng nhị phân là:</t>
+  </si>
+  <si>
+    <t>11010010</t>
+  </si>
+  <si>
+    <t>11010001</t>
+  </si>
+  <si>
+    <t>10110010</t>
+  </si>
+  <si>
+    <t>11110010</t>
+  </si>
+  <si>
+    <t>Một ứng dụng nhận dữ liệu TCP gồm các gói đến thứ tự 3, 1, 2. Căn cứ bài học, thành phần nào cho phép xác định thứ tự đúng?</t>
+  </si>
+  <si>
+    <t>Số đánh thứ tự các gói TCP.</t>
+  </si>
+  <si>
+    <t>Tên miền DNS.</t>
+  </si>
+  <si>
+    <t>Địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Mã kiểm tra Ethernet.</t>
+  </si>
+  <si>
+    <t>Khi Ethernet phát hiện lỗi truyền nhờ mã kiểm tra, theo bài máy nhận có thể:</t>
+  </si>
+  <si>
+    <t>yêu cầu gửi lại dữ liệu.</t>
+  </si>
+  <si>
+    <t>đổi IP thành DNS.</t>
+  </si>
+  <si>
+    <t>chọn cổng WAN.</t>
+  </si>
+  <si>
+    <t>đổi MAC thành TCP.</t>
+  </si>
+  <si>
+    <t>Một học sinh gọi điện thoại qua Internet và nhiều cuộc gọi cùng sử dụng một đường truyền vật lí. Nội dung bài giải thích khả năng này chủ yếu nhờ:</t>
+  </si>
+  <si>
+    <t>dữ liệu được tách thành nhiều gói, cho phép các cuộc truyền xen kẽ trên cùng đường truyền.</t>
+  </si>
+  <si>
+    <t>mỗi cuộc gọi chiếm độc quyền đường truyền.</t>
+  </si>
+  <si>
+    <t>DNS cấp một đường truyền riêng.</t>
+  </si>
+  <si>
+    <t>MAC bị loại bỏ.</t>
+  </si>
+  <si>
+    <t>Một router nhận gói đích không có trong bảng định tuyến. Nếu không có cổng mặc định được cấu hình, theo logic của ví dụ định tuyến tĩnh trong bài, điều kiện cần để router chuyển tiếp theo quy tắc mặc định là:</t>
+  </si>
+  <si>
+    <t>phải có một cổng mặc định.</t>
+  </si>
+  <si>
+    <t>phải có DNS.</t>
+  </si>
+  <si>
+    <t>phải có SMTP.</t>
+  </si>
+  <si>
+    <t>phải có địa chỉ MAC của mọi máy trên Internet.</t>
+  </si>
+  <si>
+    <t>Một máy không ping được thiết bị đích. Chỉ từ thông tin “ping không nhận Echo Reply”, có thể kết luận chắc chắn điều gì theo nội dung bài?</t>
+  </si>
+  <si>
+    <t>Không nhận được phản hồi ICMP Echo Reply từ thiết bị đích.</t>
+  </si>
+  <si>
+    <t>Chắc chắn TCP bị mất gói.</t>
+  </si>
+  <si>
+    <t>Chắc chắn DNS bị lỗi.</t>
+  </si>
+  <si>
+    <t>Chắc chắn Ethernet của mọi router bị lỗi.</t>
+  </si>
+  <si>
+    <t>Xét TCP và ứng dụng:</t>
+  </si>
+  <si>
+    <t>a) TCP cấp cho mỗi ứng dụng một số hiệu gọi là cổng ứng dụng.</t>
+  </si>
+  <si>
+    <t>b) Cổng ứng dụng giúp các gói dữ liệu được gắn nhãn để không lẫn giữa các ứng dụng.</t>
+  </si>
+  <si>
+    <t>c) Nếu hai ứng dụng cùng truyền dữ liệu, việc gắn cổng ứng dụng giúp phân biệt dữ liệu theo ứng dụng.</t>
+  </si>
+  <si>
+    <t>d) Vì có cổng ứng dụng nên TCP không cần đánh số gói và không cần cơ chế xác nhận.</t>
+  </si>
+  <si>
+    <t>Xét Ethernet và truyền gói:</t>
+  </si>
+  <si>
+    <t>a) Ethernet có quy định về khung truyền tín hiệu.</t>
+  </si>
+  <si>
+    <t>b) Việc giới hạn độ dài gói giúp tránh một lượng tin dài không giới hạn gây quá tải máy nhận.</t>
+  </si>
+  <si>
+    <t>c) Khi nhiều cuộc truyền được tách thành các gói, các cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí.</t>
+  </si>
+  <si>
+    <t>d) Việc chia thành gói khiến mỗi cuộc truyền phải độc chiếm đường truyền vật lí trong suốt thời gian truyền.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ 192.168.13.210 sang dạng nhị phân.</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00001101 11010010|11000000101010000000110111010010</t>
+  </si>
+  <si>
+    <t>Giải thích vì sao một đường truyền Internet vật lí có thể phục vụ đồng thời nhiều cuộc truyền khác nhau theo nội dung bài học.</t>
+  </si>
+  <si>
+    <t>Dữ liệu được tách thành nhiều gói, các cuộc truyền có thể xen kẽ các gói trên cùng đường truyền vật lí, giúp tận dụng đường truyền.|gói|xen kẽ</t>
+  </si>
+  <si>
+    <t>Giao thức nào trong bài quy định cách xử lí khi gửi thư điện tử từ người gửi tới máy chủ thư?</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>Địa chỉ nào được căn cứ khi truyền dữ liệu trong mạng cục bộ theo Ethernet?</t>
+  </si>
+  <si>
+    <t>Giao thức nào được coi cùng với IP là đặc thù để Internet hoạt động và tạo thành TCP/IP?</t>
+  </si>
+  <si>
+    <t>Tại sao router cần bảng định tuyến?</t>
+  </si>
+  <si>
+    <t>Để hướng dẫn nhóm địa chỉ nào sẽ gửi theo cổng nào.</t>
+  </si>
+  <si>
+    <t>Để lưu nội dung thư.</t>
+  </si>
+  <si>
+    <t>Để cấp địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Để mã hóa trang web.</t>
+  </si>
+  <si>
+    <t>Vì sao các gói TCP có thể đến nơi nhận không đúng thứ tự?</t>
+  </si>
+  <si>
+    <t>Các gói có thể được lưu ở router với thời gian khác nhau và đi theo đường khác nhau.</t>
+  </si>
+  <si>
+    <t>Vì DNS thay đổi thứ tự gói.</t>
+  </si>
+  <si>
+    <t>Vì MAC tự động đảo gói.</t>
+  </si>
+  <si>
+    <t>Vì HTTP bắt buộc gói đến ngẫu nhiên.</t>
+  </si>
+  <si>
+    <t>Tại sao DNS làm cho việc sử dụng tài nguyên mạng thuận tiện hơn?</t>
+  </si>
+  <si>
+    <t>Tên miền bằng chữ dễ nhớ hơn địa chỉ IP dài và phức tạp.</t>
+  </si>
+  <si>
+    <t>DNS làm tăng độ dài địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>DNS thay thế router.</t>
+  </si>
+  <si>
+    <t>DNS làm cho MAC có thể thay đổi.</t>
+  </si>
+  <si>
+    <t>Một địa chỉ IPv4 được viết 11000000 10101000 00001101 11010010. Giá trị byte thứ ba ở dạng thập phân là:</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Một router có chỉ dẫn nhóm X→cổng 1, nhóm Y→cổng 2. Gói thuộc X. Chọn xử lí đúng:</t>
+  </si>
+  <si>
+    <t>Gửi qua cổng 1.</t>
+  </si>
+  <si>
+    <t>Gửi qua cổng 2.</t>
+  </si>
+  <si>
+    <t>Luôn gửi qua cổng mặc định dù có chỉ dẫn.</t>
+  </si>
+  <si>
+    <t>Không thể gửi.</t>
+  </si>
+  <si>
+    <t>Một gói TCP bị thất lạc trên đường truyền. Theo bài, điều gì giúp nơi gửi biết để yêu cầu truyền lại?</t>
+  </si>
+  <si>
+    <t>Cơ chế xác nhận của TCP.</t>
+  </si>
+  <si>
+    <t>HTTP.</t>
+  </si>
+  <si>
+    <t>Một người nhận thư muốn tải thư từ hộp thư về. Trong các giao thức nêu ở bài, lựa chọn phù hợp là:</t>
+  </si>
+  <si>
+    <t>POP3 hoặc IMAP.</t>
+  </si>
+  <si>
+    <t>SMTP.</t>
+  </si>
+  <si>
+    <t>Ethernet.</t>
+  </si>
+  <si>
+    <t>IP.</t>
+  </si>
+  <si>
+    <t>Một người dùng muốn kiểm tra kết nối đến “www.google.com” bằng lệnh ping. Chuỗi chức năng phù hợp với bài là:</t>
+  </si>
+  <si>
+    <t>Tên miền có thể thay cho IP nhờ DNS; ping sử dụng ICMP để gửi Echo Request và chờ Echo Reply.</t>
+  </si>
+  <si>
+    <t>SMTP đổi tên miền thành MAC rồi ping.</t>
+  </si>
+  <si>
+    <t>TCP gửi thư tới máy chủ rồi nhận IMAP.</t>
+  </si>
+  <si>
+    <t>Ethernet tự tạo tên miền.</t>
+  </si>
+  <si>
+    <t>Một router đã đưa gói tin tới LAN đích. Để gói tới đúng máy nhận trong LAN, theo bài cần dựa vào:</t>
+  </si>
+  <si>
+    <t>địa chỉ MAC</t>
+  </si>
+  <si>
+    <t>tên miền</t>
+  </si>
+  <si>
+    <t>cổng WAN của router nguồn</t>
+  </si>
+  <si>
+    <t>Xét các giao thức thư điện tử:</t>
+  </si>
+  <si>
+    <t>a) SMTP là giao thức được nêu cho việc gửi thư.</t>
+  </si>
+  <si>
+    <t>b) POP3 hoặc IMAP là các giao thức được nêu cho việc người nhận lấy thư.</t>
+  </si>
+  <si>
+    <t>c) Nếu người gửi nhập sai địa chỉ người nhận, máy chủ thư có thể tạo thư báo lỗi chuyển ngược lại người gửi.</t>
+  </si>
+  <si>
+    <t>d) POP3/IMAP được dùng để thay thế router trong việc định tuyến thư giữa các mạng.</t>
+  </si>
+  <si>
+    <t>Xét DNS và ping:</t>
+  </si>
+  <si>
+    <t>a) ICMP được dùng trong lệnh ping theo bài.</t>
+  </si>
+  <si>
+    <t>b) DNS cho phép dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
+  </si>
+  <si>
+    <t>c) Khi ping theo tên miền, tên miền có thể được dùng thay cho IP theo chức năng DNS được nêu.</t>
+  </si>
+  <si>
+    <t>d) Nếu ping không có Echo Reply thì chắc chắn máy đích không tồn tại trên mạng.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ 192.168.1.3 sang dạng nhị phân.</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000001 00000011|11000000101010000000000100000011</t>
+  </si>
+  <si>
+    <t>Mô tả ngắn quy trình xử lí khi người gửi gửi thư đến một địa chỉ không đúng, theo ví dụ trong bài.</t>
+  </si>
+  <si>
+    <t>Máy chủ thư xử lí thư đến; nếu không có người nhận đúng địa chỉ thì tạo thư báo lỗi và chuyển ngược lại người gửi.|báo lỗi|người gửi</t>
+  </si>
+  <si>
+    <t>5 MÃ ĐỀ: 101, 202, 303, 404, 505 – Thời gian 15 phút – Ma trận mức độ theo CV 7991</t>
+  </si>
+  <si>
+    <t>Phần 1: 12 MC (C1-3 Biết, C4-6 Hiểu, C7-9 Vận dụng thấp, C10-12 Vận dụng cao) = 6 điểm</t>
+  </si>
+  <si>
+    <t>Phần 2: 2 câu TF × 4 ý (a Biết, b Hiểu, c Vận dụng thấp, d Vận dụng cao) = 2 điểm</t>
+  </si>
+  <si>
+    <t>Phần 3: 2 câu SA (C15 Vận dụng thấp, C16 Vận dụng cao) = 2 điểm</t>
+  </si>
+  <si>
+    <t>Cột I (Mã đề) dùng để hệ thống chọn ngẫu nhiên 1 trong 5 đề cho mỗi học sinh.</t>
   </si>
   <si>
     <t>NGÔ HOÀNG HẢI ANH</t>
@@ -826,7 +1639,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,15 +1659,9 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FF2752D6"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -897,15 +1704,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1239,399 +2041,399 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>359</v>
+      </c>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>360</v>
+      </c>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>361</v>
+      </c>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>362</v>
+      </c>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>363</v>
+      </c>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>364</v>
+      </c>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>365</v>
+      </c>
+      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>366</v>
+      </c>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>367</v>
+      </c>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>369</v>
+      </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>370</v>
+      </c>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>371</v>
+      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>372</v>
+      </c>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>373</v>
+      </c>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>374</v>
+      </c>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="3"/>
+        <v>375</v>
+      </c>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="3"/>
+        <v>376</v>
+      </c>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="3"/>
+        <v>377</v>
+      </c>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="3"/>
+        <v>378</v>
+      </c>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="3"/>
+        <v>379</v>
+      </c>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="3"/>
+        <v>380</v>
+      </c>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="3"/>
+        <v>381</v>
+      </c>
+      <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="3"/>
+        <v>382</v>
+      </c>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="3"/>
+        <v>383</v>
+      </c>
+      <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="3"/>
+        <v>384</v>
+      </c>
+      <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="3"/>
+        <v>385</v>
+      </c>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="3"/>
+        <v>386</v>
+      </c>
+      <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="3"/>
+        <v>387</v>
+      </c>
+      <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="3"/>
+        <v>388</v>
+      </c>
+      <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="3"/>
+        <v>389</v>
+      </c>
+      <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="3"/>
+        <v>390</v>
+      </c>
+      <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="3"/>
+        <v>391</v>
+      </c>
+      <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C35" s="3"/>
+        <v>392</v>
+      </c>
+      <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" s="3"/>
+        <v>393</v>
+      </c>
+      <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="3"/>
+        <v>394</v>
+      </c>
+      <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="3"/>
+        <v>395</v>
+      </c>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="3"/>
+        <v>396</v>
+      </c>
+      <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" s="3"/>
+        <v>397</v>
+      </c>
+      <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="3"/>
+        <v>398</v>
+      </c>
+      <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
+      <c r="A42" t="s">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
+      <c r="A43" t="s">
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
+      <c r="A44" t="s">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+      <c r="A45" t="s">
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -1639,7 +2441,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -1647,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>134</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -1655,7 +2457,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -1663,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -1671,7 +2473,7 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -1679,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -1687,7 +2489,7 @@
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -1695,7 +2497,7 @@
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -1703,7 +2505,7 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -1711,7 +2513,7 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -1719,7 +2521,7 @@
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -1727,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -1735,7 +2537,7 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -1743,7 +2545,7 @@
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -1751,7 +2553,7 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
@@ -1759,7 +2561,7 @@
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -1767,7 +2569,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -1775,7 +2577,7 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -1783,7 +2585,7 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -1791,7 +2593,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -1799,7 +2601,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>424</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -1807,7 +2609,7 @@
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
@@ -1815,7 +2617,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -1823,7 +2625,7 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>156</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -1831,7 +2633,7 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -1839,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -1847,7 +2649,7 @@
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -1855,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>431</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -1863,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>432</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -1871,7 +2673,7 @@
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>433</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -1879,7 +2681,7 @@
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>434</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -1887,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>435</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -1895,7 +2697,7 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -1903,7 +2705,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>437</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -1911,7 +2713,7 @@
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -1919,7 +2721,7 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>168</v>
+        <v>439</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -1927,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -1935,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>441</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -1943,7 +2745,7 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>442</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -1951,7 +2753,7 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>443</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -1959,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>444</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -1967,7 +2769,7 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>445</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -1975,7 +2777,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>446</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -1983,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -1991,7 +2793,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>448</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -1999,7 +2801,7 @@
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -2007,7 +2809,7 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
+        <v>450</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -2015,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -2023,7 +2825,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>452</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -2031,7 +2833,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>453</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -2039,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>183</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -2047,7 +2849,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>455</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -2055,7 +2857,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>185</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -2063,7 +2865,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>457</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -2071,7 +2873,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>458</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -2079,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>188</v>
+        <v>459</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -2087,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>189</v>
+        <v>460</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -2095,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>190</v>
+        <v>461</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -2103,7 +2905,7 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>191</v>
+        <v>462</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -2111,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>192</v>
+        <v>463</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -2119,7 +2921,7 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>193</v>
+        <v>464</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -2127,7 +2929,7 @@
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>194</v>
+        <v>465</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -2135,7 +2937,7 @@
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>466</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -2143,7 +2945,7 @@
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>196</v>
+        <v>467</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -2151,7 +2953,7 @@
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>197</v>
+        <v>468</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -2159,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>198</v>
+        <v>469</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -2167,7 +2969,7 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>199</v>
+        <v>470</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -2175,7 +2977,7 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>200</v>
+        <v>471</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -2183,7 +2985,7 @@
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>201</v>
+        <v>472</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -2191,7 +2993,7 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>473</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -2199,7 +3001,7 @@
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -2207,7 +3009,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>475</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -2215,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>205</v>
+        <v>476</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -2223,7 +3025,7 @@
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>206</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -2231,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>478</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -2239,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>479</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -2247,7 +3049,7 @@
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2255,7 +3057,7 @@
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>210</v>
+        <v>481</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -2263,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>482</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -2271,7 +3073,7 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>212</v>
+        <v>483</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -2279,7 +3081,7 @@
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>213</v>
+        <v>484</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -2287,7 +3089,7 @@
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>214</v>
+        <v>485</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -2295,7 +3097,7 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>215</v>
+        <v>486</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -2303,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>216</v>
+        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -2311,7 +3113,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>217</v>
+        <v>488</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -2319,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>489</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -2327,7 +3129,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>219</v>
+        <v>490</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -2335,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>220</v>
+        <v>491</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -2343,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>221</v>
+        <v>492</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -2351,7 +3153,7 @@
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>222</v>
+        <v>493</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -2359,7 +3161,7 @@
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>223</v>
+        <v>494</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -2367,7 +3169,7 @@
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>495</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -2375,7 +3177,7 @@
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>225</v>
+        <v>496</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -2383,7 +3185,7 @@
         <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>226</v>
+        <v>497</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -2391,7 +3193,7 @@
         <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>227</v>
+        <v>498</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -2399,7 +3201,7 @@
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>228</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -2407,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>229</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -2415,7 +3217,7 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>230</v>
+        <v>501</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -2423,7 +3225,7 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>231</v>
+        <v>502</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -2431,7 +3233,7 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>232</v>
+        <v>503</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -2439,7 +3241,7 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>233</v>
+        <v>504</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -2447,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>234</v>
+        <v>505</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -2455,7 +3257,7 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>235</v>
+        <v>506</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -2463,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>236</v>
+        <v>507</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -2471,7 +3273,7 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>237</v>
+        <v>508</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -2479,7 +3281,7 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>238</v>
+        <v>509</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -2487,7 +3289,7 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>239</v>
+        <v>510</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -2495,7 +3297,7 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>240</v>
+        <v>511</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -2503,7 +3305,7 @@
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>241</v>
+        <v>512</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -2511,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>242</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -2519,7 +3321,7 @@
         <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>243</v>
+        <v>514</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -2527,7 +3329,7 @@
         <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>244</v>
+        <v>515</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -2535,7 +3337,7 @@
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>245</v>
+        <v>516</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -2543,7 +3345,7 @@
         <v>6</v>
       </c>
       <c r="B160" t="s">
-        <v>246</v>
+        <v>517</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -2551,7 +3353,7 @@
         <v>6</v>
       </c>
       <c r="B161" t="s">
-        <v>247</v>
+        <v>518</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -2559,7 +3361,7 @@
         <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>248</v>
+        <v>519</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -2567,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>249</v>
+        <v>520</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -2575,7 +3377,7 @@
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>250</v>
+        <v>521</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -2583,7 +3385,7 @@
         <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>251</v>
+        <v>522</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -2591,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>252</v>
+        <v>523</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -2599,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>253</v>
+        <v>524</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -2607,7 +3409,7 @@
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>254</v>
+        <v>525</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -2615,7 +3417,7 @@
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>255</v>
+        <v>526</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -2623,7 +3425,7 @@
         <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>256</v>
+        <v>527</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -2631,7 +3433,7 @@
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>257</v>
+        <v>528</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -2639,7 +3441,7 @@
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>258</v>
+        <v>529</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -2647,7 +3449,7 @@
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>259</v>
+        <v>530</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -2655,7 +3457,7 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>260</v>
+        <v>531</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -2663,7 +3465,7 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>261</v>
+        <v>532</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -2671,7 +3473,7 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>262</v>
+        <v>533</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -2679,7 +3481,7 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>263</v>
+        <v>534</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -2687,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>264</v>
+        <v>535</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -2695,400 +3497,2293 @@
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>265</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="7" width="35" customWidth="1"/>
+    <col min="4" max="7" width="32" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="I3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="F6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="B14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="B15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="B30" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="B31" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>3</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>3</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
         <v>2</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="B46" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>2</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="B48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
         <v>3</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="B49" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A58" s="4">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A60" s="4">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4">
+        <v>2</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
+        <v>2</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
         <v>3</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B64" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
+        <v>3</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A66" s="4">
+        <v>1</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>1</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>1</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="E68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>1</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A72" s="4">
+        <v>1</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A74" s="4">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="4">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A78" s="4">
+        <v>2</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
+        <v>2</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="4">
         <v>3</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="B80" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
         <v>3</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
-        <v>81</v>
+      <c r="B81" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3101,37 +5796,32 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
-        <v>82</v>
+    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>86</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/data/Mau_De_KTTX_Tin12_Bai4.xlsx
+++ b/data/Mau_De_KTTX_Tin12_Bai4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHU NHIEM\26-27-B9\QUY DINH DANH MUC WEBH2T GITBUH IO\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72405EA8-E12B-4E8B-A573-308A7BFBBBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3019E3-66CB-41C4-9314-BA16E1896CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HocSinh" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="534">
   <si>
     <t>Lớp</t>
   </si>
@@ -174,9 +174,6 @@
     <t>Để biến tên miền thành địa chỉ IP.</t>
   </si>
   <si>
-    <t>Một máy A gửi dữ liệu tới máy B ở LAN khác. Theo bài học, quá trình phù hợp nhất là:</t>
-  </si>
-  <si>
     <t>A gửi trực tiếp bằng MAC của B trên toàn Internet.</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>Gửi đồng thời cả 3 cổng.</t>
   </si>
   <si>
-    <t>Một ứng dụng gửi nhiều gói qua các router khác nhau nên gói sau có thể đến trước gói trước. Cơ chế nào trong bài giúp xử lí tình huống này?</t>
-  </si>
-  <si>
     <t>DNS đổi tên gói tin.</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>Chuyển gói sang DNS để tìm đường.</t>
   </si>
   <si>
-    <t>Một người dùng biết địa chỉ IP máy chủ nhưng khó nhớ dãy số. Họ muốn sử dụng một tên bằng chữ thay thế địa chỉ IP. Giao thức phù hợp theo bài là:</t>
-  </si>
-  <si>
     <t>TCP</t>
   </si>
   <si>
@@ -306,15 +297,6 @@
     <t>192.168.1.3</t>
   </si>
   <si>
-    <t>Một máy gửi dữ liệu đến máy ở LAN khác. Hãy nêu chuỗi xử lí chính theo bài học, từ khi dữ liệu rời máy gửi đến khi được chuyển tới máy nhận.</t>
-  </si>
-  <si>
-    <t>Dựa trên IP để router chuyển tiếp tới LAN đích; khi đến LAN đích, dùng MAC để chuyển tới máy nhận.|IP router LAN đích MAC</t>
-  </si>
-  <si>
-    <t>Giao thức truyền tin trong mạng cục bộ được nêu trong bài là:</t>
-  </si>
-  <si>
     <t>HTTP</t>
   </si>
   <si>
@@ -354,9 +336,6 @@
     <t>Để mọi dữ liệu chỉ đi qua một đường truyền.</t>
   </si>
   <si>
-    <t>Theo bài, tại sao TCP cần cơ chế xác nhận?</t>
-  </si>
-  <si>
     <t>Để nơi gửi biết gói tin có sai sót hoặc thất lạc và yêu cầu gửi lại khi cần.</t>
   </si>
   <si>
@@ -399,9 +378,6 @@
     <t>11000000 10101000 00000010 00000011</t>
   </si>
   <si>
-    <t>Một thiết bị nhận dữ liệu trong LAN nhưng địa chỉ MAC đích của khung không trùng với MAC của thiết bị đó. Theo mô tả trong bài, thiết bị đó:</t>
-  </si>
-  <si>
     <t>Nhận khung vì IP trùng.</t>
   </si>
   <si>
@@ -414,9 +390,6 @@
     <t>Đổi MAC thành IP rồi nhận.</t>
   </si>
   <si>
-    <t>Khi ping một thiết bị, theo bài công cụ ping gửi loại yêu cầu nào?</t>
-  </si>
-  <si>
     <t>HTTP Request</t>
   </si>
   <si>
@@ -432,9 +405,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>Một học sinh nhập ping www.google.com. Theo bài, tên miền trong lệnh ping có thể được dùng thay cho địa chỉ IP nhờ cơ chế của:</t>
-  </si>
-  <si>
     <t>Một router có nhiều cổng WAN. Gói tin đến có địa chỉ thuộc nhóm được chỉ dẫn đi qua cổng 4. Router nên xử lí thế nào?</t>
   </si>
   <si>
@@ -450,9 +420,6 @@
     <t>Đổi IP thành MAC rồi dừng chuyển tiếp.</t>
   </si>
   <si>
-    <t>Hai gói dữ liệu của cùng một ứng dụng đi theo các đường khác nhau và gói B đến trước gói A. Theo bài, xử lí nào phù hợp nhất?</t>
-  </si>
-  <si>
     <t>TCP dùng số thứ tự để ráp dữ liệu về đúng thứ tự.</t>
   </si>
   <si>
@@ -501,12 +468,6 @@
     <t>10000011 11010110 00010111 00010000|10000011110101100001011100010000</t>
   </si>
   <si>
-    <t>Một người dùng muốn truy cập tài nguyên bằng tên “moet.edu.vn” thay vì nhớ địa chỉ IP. Giải thích giao thức nào hỗ trợ cách sử dụng này và lợi ích chính là gì.</t>
-  </si>
-  <si>
-    <t>DNS; giúp dùng tên bằng chữ dễ nhớ thay cho địa chỉ IP khó nhớ.|DNS</t>
-  </si>
-  <si>
     <t>Giao thức được nêu để quy định cách biểu diễn (mã hóa) các trang web là:</t>
   </si>
   <si>
@@ -687,21 +648,12 @@
     <t>Đổi địa chỉ 00001010 00011001 00000000 11111111 sang dạng thập phân.</t>
   </si>
   <si>
-    <t>Trong một phiên truyền, các gói dữ liệu đến router có thể đi các đường khác nhau và đến nơi nhận không đúng thứ tự. Hãy nêu hai cơ chế TCP trong bài giúp dữ liệu được truyền tin cậy.</t>
-  </si>
-  <si>
-    <t>Đánh số gói để ráp đúng thứ tự; cơ chế xác nhận để phát hiện sai sót/thất lạc và yêu cầu gửi lại khi cần.|đánh số|xác nhận</t>
-  </si>
-  <si>
     <t>Giao thức nào được nêu là giao thức định tuyến/chọn đường?</t>
   </si>
   <si>
     <t>404</t>
   </si>
   <si>
-    <t>Tên đầy đủ của TCP trong bài là:</t>
-  </si>
-  <si>
     <t>Transmission Control Protocol</t>
   </si>
   <si>
@@ -900,12 +852,6 @@
     <t>11000000 10101000 00001101 11010010|11000000101010000000110111010010</t>
   </si>
   <si>
-    <t>Giải thích vì sao một đường truyền Internet vật lí có thể phục vụ đồng thời nhiều cuộc truyền khác nhau theo nội dung bài học.</t>
-  </si>
-  <si>
-    <t>Dữ liệu được tách thành nhiều gói, các cuộc truyền có thể xen kẽ các gói trên cùng đường truyền vật lí, giúp tận dụng đường truyền.|gói|xen kẽ</t>
-  </si>
-  <si>
     <t>Giao thức nào trong bài quy định cách xử lí khi gửi thư điện tử từ người gửi tới máy chủ thư?</t>
   </si>
   <si>
@@ -993,18 +939,12 @@
     <t>Không thể gửi.</t>
   </si>
   <si>
-    <t>Một gói TCP bị thất lạc trên đường truyền. Theo bài, điều gì giúp nơi gửi biết để yêu cầu truyền lại?</t>
-  </si>
-  <si>
     <t>Cơ chế xác nhận của TCP.</t>
   </si>
   <si>
     <t>HTTP.</t>
   </si>
   <si>
-    <t>Một người nhận thư muốn tải thư từ hộp thư về. Trong các giao thức nêu ở bài, lựa chọn phù hợp là:</t>
-  </si>
-  <si>
     <t>POP3 hoặc IMAP.</t>
   </si>
   <si>
@@ -1017,9 +957,6 @@
     <t>IP.</t>
   </si>
   <si>
-    <t>Một người dùng muốn kiểm tra kết nối đến “www.google.com” bằng lệnh ping. Chuỗi chức năng phù hợp với bài là:</t>
-  </si>
-  <si>
     <t>Tên miền có thể thay cho IP nhờ DNS; ping sử dụng ICMP để gửi Echo Request và chờ Echo Reply.</t>
   </si>
   <si>
@@ -1032,9 +969,6 @@
     <t>Ethernet tự tạo tên miền.</t>
   </si>
   <si>
-    <t>Một router đã đưa gói tin tới LAN đích. Để gói tới đúng máy nhận trong LAN, theo bài cần dựa vào:</t>
-  </si>
-  <si>
     <t>địa chỉ MAC</t>
   </si>
   <si>
@@ -1080,12 +1014,6 @@
     <t>11000000 10101000 00000001 00000011|11000000101010000000000100000011</t>
   </si>
   <si>
-    <t>Mô tả ngắn quy trình xử lí khi người gửi gửi thư đến một địa chỉ không đúng, theo ví dụ trong bài.</t>
-  </si>
-  <si>
-    <t>Máy chủ thư xử lí thư đến; nếu không có người nhận đúng địa chỉ thì tạo thư báo lỗi và chuyển ngược lại người gửi.|báo lỗi|người gửi</t>
-  </si>
-  <si>
     <t>5 MÃ ĐỀ: 101, 202, 303, 404, 505 – Thời gian 15 phút – Ma trận mức độ theo CV 7991</t>
   </si>
   <si>
@@ -1633,13 +1561,178 @@
   </si>
   <si>
     <t>NGUYỄN LÂM HOÀNG VŨ</t>
+  </si>
+  <si>
+    <t>Một máy A gửi dữ liệu tới máy B ở LAN khác. Theo bạn, quá trình phù hợp nhất là:</t>
+  </si>
+  <si>
+    <t>Một ứng dụng gửi nhiều gói qua các router khác nhau nên gói sau có thể đến trước gói trước. Cơ chế nào giúp xử lí tình huống này?</t>
+  </si>
+  <si>
+    <t>Một người dùng biết địa chỉ IP máy chủ nhưng khó nhớ dãy số. Họ muốn sử dụng một tên bằng chữ thay thế địa chỉ IP. Giao thức phù hợp là:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cho tên miền </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>. Theo cách phân lớp tên miền, hãy xác định tên miền cấp cao nhất (TLD)</t>
+    </r>
+  </si>
+  <si>
+    <t>.com</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cho tên miền </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>blog.example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>. Hãy xác định subdomain</t>
+    </r>
+  </si>
+  <si>
+    <t>blog</t>
+  </si>
+  <si>
+    <t>Giao thức truyền tin trong mạng cục bộ là:</t>
+  </si>
+  <si>
+    <t>Tại sao TCP cần cơ chế xác nhận?</t>
+  </si>
+  <si>
+    <t>Một thiết bị nhận dữ liệu trong LAN nhưng địa chỉ MAC đích của khung không trùng với MAC của thiết bị đó. Theo mô tả thiết bị đó:</t>
+  </si>
+  <si>
+    <t>Khi ping một thiết bị, công cụ ping gửi loại yêu cầu nào?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Một học sinh nhập ping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>www.google.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>. Tên miền trong lệnh ping có thể được dùng thay cho địa chỉ IP nhờ cơ chế của:</t>
+    </r>
+  </si>
+  <si>
+    <t>Hai gói dữ liệu của cùng một ứng dụng đi theo các đường khác nhau và gói B đến trước gói A. Xử lí nào phù hợp nhất?</t>
+  </si>
+  <si>
+    <t>Tên đầy đủ của TCP là:</t>
+  </si>
+  <si>
+    <t>Một người dùng muốn gửi một email đến người khác. Trong ba giao thức SMTP, POP3, IMAP, giao thức nào được sử dụng cho hoạt động gửi email?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Một hệ thống thư điện tử cần thực hiện hai chức năng: gửi thư từ người gửi đến máy chủ thư và nhận thư từ máy chủ về cho người dùng. Hãy xác định giao thức phù hợp cho chức năng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Nhận thư</t>
+    </r>
+  </si>
+  <si>
+    <t>Một gói TCP bị thất lạc trên đường truyền. Điều gì giúp nơi gửi biết để yêu cầu truyền lại?</t>
+  </si>
+  <si>
+    <t>Một người nhận thư muốn tải thư từ hộp thư về. Trong các giao thức, lựa chọn phù hợp là:</t>
+  </si>
+  <si>
+    <r>
+      <t>Một người dùng muốn kiểm tra kết nối đến “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>www.google.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>” bằng lệnh ping. Chuỗi chức năng phù hợp là:</t>
+    </r>
+  </si>
+  <si>
+    <t>Một router đã đưa gói tin tới LAN đích. Để gói tới đúng máy nhận trong LAN, theo bạn cần dựa vào:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cho tên miền </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>www.example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Giao thức nào có chức năng chuyển đổi tên miền dễ nhớ thành địa chỉ IP để máy tính có thể xác định máy chủ cần truy cập?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1662,6 +1755,17 @@
       <sz val="12"/>
       <color rgb="FF2752D6"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1704,7 +1808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1715,6 +1819,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2041,7 +2151,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -2050,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -2059,7 +2169,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -2068,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="C5" s="2"/>
     </row>
@@ -2077,7 +2187,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -2086,7 +2196,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -2095,7 +2205,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -2104,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C9" s="2"/>
     </row>
@@ -2113,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C10" s="2"/>
     </row>
@@ -2122,7 +2232,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -2131,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -2140,7 +2250,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -2149,7 +2259,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -2158,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C15" s="2"/>
     </row>
@@ -2167,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -2176,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C17" s="2"/>
     </row>
@@ -2185,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="C18" s="2"/>
     </row>
@@ -2194,7 +2304,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C19" s="2"/>
     </row>
@@ -2203,7 +2313,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -2212,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="C21" s="2"/>
     </row>
@@ -2221,7 +2331,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -2230,7 +2340,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="C23" s="2"/>
     </row>
@@ -2239,7 +2349,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -2248,7 +2358,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="C25" s="2"/>
     </row>
@@ -2257,7 +2367,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C26" s="2"/>
     </row>
@@ -2266,7 +2376,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="C27" s="2"/>
     </row>
@@ -2275,7 +2385,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="C28" s="2"/>
     </row>
@@ -2284,7 +2394,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="C29" s="2"/>
     </row>
@@ -2293,7 +2403,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="C30" s="2"/>
     </row>
@@ -2302,7 +2412,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="C31" s="2"/>
     </row>
@@ -2311,7 +2421,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="C32" s="2"/>
     </row>
@@ -2320,7 +2430,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C33" s="2"/>
     </row>
@@ -2329,7 +2439,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
     </row>
@@ -2338,7 +2448,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
     </row>
@@ -2347,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="C36" s="2"/>
     </row>
@@ -2356,7 +2466,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="C37" s="2"/>
     </row>
@@ -2365,7 +2475,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
     </row>
@@ -2374,7 +2484,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
     </row>
@@ -2383,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
     </row>
@@ -2392,7 +2502,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
     </row>
@@ -2401,7 +2511,7 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -2409,7 +2519,7 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -2417,7 +2527,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -2425,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -2433,7 +2543,7 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -2441,7 +2551,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -2449,7 +2559,7 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -2457,7 +2567,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -2465,7 +2575,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -2473,7 +2583,7 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -2481,7 +2591,7 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -2489,7 +2599,7 @@
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -2497,7 +2607,7 @@
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -2505,7 +2615,7 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -2513,7 +2623,7 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -2521,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -2529,7 +2639,7 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -2537,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -2545,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -2553,7 +2663,7 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
@@ -2561,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -2569,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -2577,7 +2687,7 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -2585,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -2593,7 +2703,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -2601,7 +2711,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -2609,7 +2719,7 @@
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
@@ -2617,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -2625,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -2633,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -2641,7 +2751,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -2649,7 +2759,7 @@
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -2657,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -2665,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -2673,7 +2783,7 @@
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -2681,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -2689,7 +2799,7 @@
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -2697,7 +2807,7 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -2705,7 +2815,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -2713,7 +2823,7 @@
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -2721,7 +2831,7 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -2729,7 +2839,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -2737,7 +2847,7 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -2745,7 +2855,7 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -2753,7 +2863,7 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -2761,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -2769,7 +2879,7 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -2777,7 +2887,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -2785,7 +2895,7 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -2793,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -2801,7 +2911,7 @@
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -2809,7 +2919,7 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -2817,7 +2927,7 @@
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -2825,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -2833,7 +2943,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -2841,7 +2951,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -2849,7 +2959,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -2857,7 +2967,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -2865,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -2873,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -2881,7 +2991,7 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -2889,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -2897,7 +3007,7 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -2905,7 +3015,7 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -2913,7 +3023,7 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -2921,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -2929,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -2937,7 +3047,7 @@
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -2945,7 +3055,7 @@
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -2953,7 +3063,7 @@
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -2961,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -2969,7 +3079,7 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -2977,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -2985,7 +3095,7 @@
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -2993,7 +3103,7 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -3001,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -3009,7 +3119,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -3017,7 +3127,7 @@
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -3025,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -3033,7 +3143,7 @@
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -3041,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -3049,7 +3159,7 @@
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -3057,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -3065,7 +3175,7 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -3073,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -3081,7 +3191,7 @@
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -3089,7 +3199,7 @@
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -3097,7 +3207,7 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -3105,7 +3215,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -3113,7 +3223,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -3121,7 +3231,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -3129,7 +3239,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -3137,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -3145,7 +3255,7 @@
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -3153,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -3161,7 +3271,7 @@
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -3169,7 +3279,7 @@
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -3177,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -3185,7 +3295,7 @@
         <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -3193,7 +3303,7 @@
         <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -3201,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -3209,7 +3319,7 @@
         <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -3217,7 +3327,7 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>501</v>
+        <v>477</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -3225,7 +3335,7 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -3233,7 +3343,7 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -3241,7 +3351,7 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -3249,7 +3359,7 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -3257,7 +3367,7 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -3265,7 +3375,7 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -3273,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -3281,7 +3391,7 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -3289,7 +3399,7 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -3297,7 +3407,7 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -3305,7 +3415,7 @@
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -3313,7 +3423,7 @@
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -3321,7 +3431,7 @@
         <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -3329,7 +3439,7 @@
         <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -3337,7 +3447,7 @@
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -3345,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="B160" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -3353,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="B161" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -3361,7 +3471,7 @@
         <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -3369,7 +3479,7 @@
         <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -3377,7 +3487,7 @@
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -3385,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -3393,7 +3503,7 @@
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -3401,7 +3511,7 @@
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -3409,7 +3519,7 @@
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -3417,7 +3527,7 @@
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -3425,7 +3535,7 @@
         <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -3433,7 +3543,7 @@
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>528</v>
+        <v>504</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -3441,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -3449,7 +3559,7 @@
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -3457,7 +3567,7 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>531</v>
+        <v>507</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -3465,7 +3575,7 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -3473,7 +3583,7 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -3481,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>534</v>
+        <v>510</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -3489,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -3497,7 +3607,7 @@
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -3728,19 +3838,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>29</v>
@@ -3757,19 +3867,19 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>29</v>
@@ -3778,7 +3888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>1</v>
       </c>
@@ -3786,19 +3896,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>29</v>
@@ -3815,19 +3925,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>29</v>
@@ -3844,19 +3954,19 @@
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>29</v>
@@ -3873,19 +3983,19 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>75</v>
+        <v>515</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>29</v>
@@ -3899,25 +4009,25 @@
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>23</v>
@@ -3928,25 +4038,25 @@
         <v>2</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="H15" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>23</v>
@@ -3957,38 +4067,38 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>516</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>95</v>
+      <c r="H17" s="6" t="s">
+        <v>517</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>23</v>
@@ -4001,17 +4111,17 @@
       <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>96</v>
+      <c r="C18" s="6" t="s">
+        <v>520</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>26</v>
@@ -4020,7 +4130,7 @@
         <v>22</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -4031,25 +4141,25 @@
         <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -4060,16 +4170,16 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>27</v>
@@ -4078,7 +4188,7 @@
         <v>22</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4089,25 +4199,25 @@
         <v>16</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4117,26 +4227,26 @@
       <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
+      <c r="C22" s="6" t="s">
+        <v>521</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4147,25 +4257,25 @@
         <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4176,25 +4286,25 @@
         <v>16</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4204,26 +4314,26 @@
       <c r="B25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>125</v>
+      <c r="C25" s="6" t="s">
+        <v>522</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -4233,46 +4343,46 @@
       <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>130</v>
+      <c r="C26" s="6" t="s">
+        <v>523</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>1</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>136</v>
+      <c r="C27" s="6" t="s">
+        <v>524</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>26</v>
@@ -4281,7 +4391,7 @@
         <v>22</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4292,25 +4402,25 @@
         <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4320,26 +4430,26 @@
       <c r="B29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>142</v>
+      <c r="C29" s="6" t="s">
+        <v>525</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="50" x14ac:dyDescent="0.35">
@@ -4347,28 +4457,28 @@
         <v>2</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="50" x14ac:dyDescent="0.35">
@@ -4376,28 +4486,28 @@
         <v>2</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4405,41 +4515,41 @@
         <v>3</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>3</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>159</v>
+        <v>88</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>518</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="4" t="s">
-        <v>160</v>
+      <c r="H33" s="6" t="s">
+        <v>519</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4450,25 +4560,25 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -4479,25 +4589,25 @@
         <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4508,25 +4618,25 @@
         <v>16</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4537,25 +4647,25 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4566,25 +4676,25 @@
         <v>16</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4595,25 +4705,25 @@
         <v>16</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4624,25 +4734,25 @@
         <v>16</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4653,25 +4763,25 @@
         <v>16</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -4682,25 +4792,25 @@
         <v>16</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -4711,25 +4821,25 @@
         <v>16</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -4740,25 +4850,25 @@
         <v>16</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -4769,25 +4879,25 @@
         <v>16</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4795,28 +4905,28 @@
         <v>2</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4824,28 +4934,28 @@
         <v>2</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -4853,41 +4963,41 @@
         <v>3</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>3</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>221</v>
+        <v>88</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>527</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="4" t="s">
-        <v>222</v>
+      <c r="H49" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -4898,10 +5008,10 @@
         <v>16</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>26</v>
@@ -4910,13 +5020,13 @@
         <v>25</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -4926,26 +5036,26 @@
       <c r="B51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>225</v>
+      <c r="C51" s="6" t="s">
+        <v>526</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4956,25 +5066,25 @@
         <v>16</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -4985,25 +5095,25 @@
         <v>16</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5014,25 +5124,25 @@
         <v>16</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5043,25 +5153,25 @@
         <v>16</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5072,25 +5182,25 @@
         <v>16</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5101,25 +5211,25 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5130,25 +5240,25 @@
         <v>16</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5159,25 +5269,25 @@
         <v>16</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="50" x14ac:dyDescent="0.35">
@@ -5188,25 +5298,25 @@
         <v>16</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5217,25 +5327,25 @@
         <v>16</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5243,28 +5353,28 @@
         <v>2</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5272,28 +5382,28 @@
         <v>2</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5301,41 +5411,41 @@
         <v>3</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="62.5" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="38" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>3</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>292</v>
+        <v>88</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>528</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="4" t="s">
-        <v>293</v>
+      <c r="H65" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5346,7 +5456,7 @@
         <v>16</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>26</v>
@@ -5364,7 +5474,7 @@
         <v>22</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5375,25 +5485,25 @@
         <v>16</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5404,25 +5514,25 @@
         <v>16</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5433,25 +5543,25 @@
         <v>16</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5462,25 +5572,25 @@
         <v>16</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5491,25 +5601,25 @@
         <v>16</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5520,25 +5630,25 @@
         <v>16</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5549,25 +5659,25 @@
         <v>16</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5577,26 +5687,26 @@
       <c r="B74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>323</v>
+      <c r="C74" s="6" t="s">
+        <v>529</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5606,26 +5716,26 @@
       <c r="B75" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>326</v>
+      <c r="C75" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5635,26 +5745,26 @@
       <c r="B76" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>331</v>
+      <c r="C76" s="6" t="s">
+        <v>531</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="25" x14ac:dyDescent="0.35">
@@ -5664,26 +5774,26 @@
       <c r="B77" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>336</v>
+      <c r="C77" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="50" x14ac:dyDescent="0.35">
@@ -5691,28 +5801,28 @@
         <v>2</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5720,28 +5830,28 @@
         <v>2</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
@@ -5749,41 +5859,41 @@
         <v>3</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="62.5" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="38" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>3</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>352</v>
+        <v>88</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>533</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="4" t="s">
-        <v>353</v>
+      <c r="H81" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5801,27 +5911,27 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/data/Mau_De_KTTX_Tin12_Bai4.xlsx
+++ b/data/Mau_De_KTTX_Tin12_Bai4.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHU NHIEM\26-27-B9\QUY DINH DANH MUC WEBH2T GITBUH IO\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3019E3-66CB-41C4-9314-BA16E1896CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200751D7-5876-474A-A0BF-4764B9AEF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HocSinh" sheetId="1" r:id="rId1"/>
     <sheet name="CauHoi" sheetId="2" r:id="rId2"/>
     <sheet name="HuongDan" sheetId="3" r:id="rId3"/>
+    <sheet name="LichThi" sheetId="4" r:id="rId4"/>
+    <sheet name="HuongDan_Lich" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="541">
   <si>
     <t>Lớp</t>
   </si>
@@ -1726,6 +1728,27 @@
       </rPr>
       <t>. Giao thức nào có chức năng chuyển đổi tên miền dễ nhớ thành địa chỉ IP để máy tính có thể xác định máy chủ cần truy cập?</t>
     </r>
+  </si>
+  <si>
+    <t>Từ</t>
+  </si>
+  <si>
+    <t>Đến</t>
+  </si>
+  <si>
+    <t>2026-10-05T08:00</t>
+  </si>
+  <si>
+    <t>2026-10-05T17:00</t>
+  </si>
+  <si>
+    <t>Sheet LichThi: mỗi dòng = một suất thi. Cột Từ/Đến dùng định dạng 2026-10-07T07:00 (năm-tháng-ngàyTgiờ:phút).</t>
+  </si>
+  <si>
+    <t>Upload file Excel này lên GitHub data/ → mọi máy tải trang thi sẽ cùng thấy khung giờ.</t>
+  </si>
+  <si>
+    <t>Trên trang GV có nút «Tải lịch .xlsx» để xuất lịch hiện tại.</t>
   </si>
 </sst>
 </file>
@@ -1768,7 +1791,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1778,6 +1801,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2752D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0369A1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1808,7 +1836,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1825,6 +1853,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5937,4 +5966,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672EBABE-4377-4EE0-99D1-ED1DD8A96285}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D65FB64-43B5-4101-A4E1-D57ABE446BD8}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Mau_De_KTTX_Tin12_Bai4.xlsx
+++ b/data/Mau_De_KTTX_Tin12_Bai4.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHU NHIEM\26-27-B9\QUY DINH DANH MUC WEBH2T GITBUH IO\KIEM TRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAM\KTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200751D7-5876-474A-A0BF-4764B9AEF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED1567A-3438-429E-ABF3-396713CF7983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14490" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HocSinh" sheetId="1" r:id="rId1"/>
     <sheet name="CauHoi" sheetId="2" r:id="rId2"/>
-    <sheet name="HuongDan" sheetId="3" r:id="rId3"/>
-    <sheet name="LichThi" sheetId="4" r:id="rId4"/>
+    <sheet name="LichThi" sheetId="3" r:id="rId3"/>
+    <sheet name="HuongDan" sheetId="4" r:id="rId4"/>
     <sheet name="HuongDan_Lich" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -308,9 +308,552 @@
     <t>Địa chỉ gắn với phần cứng, được mô tả dài 6 byte là:</t>
   </si>
   <si>
+    <t>Giao thức kiểm soát việc truyền dữ liệu có tên viết tắt là:</t>
+  </si>
+  <si>
+    <t>Tại sao truyền dữ liệu Ethernet theo từng gói có độ dài xác định?</t>
+  </si>
+  <si>
+    <t>Để tránh một lượng tin dài không giới hạn làm quá tải máy nhận và cản trở các cuộc truyền khác.</t>
+  </si>
+  <si>
+    <t>Để thay thế địa chỉ MAC bằng tên miền.</t>
+  </si>
+  <si>
+    <t>Để router không cần bảng định tuyến.</t>
+  </si>
+  <si>
+    <t>Để mọi dữ liệu chỉ đi qua một đường truyền.</t>
+  </si>
+  <si>
+    <t>Để nơi gửi biết gói tin có sai sót hoặc thất lạc và yêu cầu gửi lại khi cần.</t>
+  </si>
+  <si>
+    <t>Để xác định tên miền cấp cao nhất.</t>
+  </si>
+  <si>
+    <t>Để tạo địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Để quy định cách mã hóa trang web.</t>
+  </si>
+  <si>
+    <t>Vì sao nhiều cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí khi dữ liệu được tách thành gói?</t>
+  </si>
+  <si>
+    <t>Vì từng gói của các cuộc truyền có thể được truyền xen kẽ, giúp tận dụng đường truyền.</t>
+  </si>
+  <si>
+    <t>Vì mỗi cuộc truyền được cấp một đường vật lí riêng.</t>
+  </si>
+  <si>
+    <t>Vì router không cần chọn cổng.</t>
+  </si>
+  <si>
+    <t>Vì DNS chia đường truyền thành các tên miền.</t>
+  </si>
+  <si>
+    <t>Một máy có IP 192.168.1.3. Dạng nhị phân tương ứng là:</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000001 00000011</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000011 00000001</t>
+  </si>
+  <si>
+    <t>11000000 10101001 00000001 00000011</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00000010 00000011</t>
+  </si>
+  <si>
+    <t>Nhận khung vì IP trùng.</t>
+  </si>
+  <si>
+    <t>Không nhận khung đó vì trong LAN máy tính nhận các gói có MAC đích trùng MAC của mình.</t>
+  </si>
+  <si>
+    <t>Luôn chuyển khung cho DNS.</t>
+  </si>
+  <si>
+    <t>Đổi MAC thành IP rồi nhận.</t>
+  </si>
+  <si>
+    <t>HTTP Request</t>
+  </si>
+  <si>
+    <t>SMTP Request</t>
+  </si>
+  <si>
+    <t>ICMP Echo Request</t>
+  </si>
+  <si>
+    <t>DNS Request</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Một router có nhiều cổng WAN. Gói tin đến có địa chỉ thuộc nhóm được chỉ dẫn đi qua cổng 4. Router nên xử lí thế nào?</t>
+  </si>
+  <si>
+    <t>Chọn cổng 4 để gửi tiếp.</t>
+  </si>
+  <si>
+    <t>Chỉ dùng cổng mặc định dù đã có chỉ dẫn.</t>
+  </si>
+  <si>
+    <t>Gửi qua mọi cổng WAN.</t>
+  </si>
+  <si>
+    <t>Đổi IP thành MAC rồi dừng chuyển tiếp.</t>
+  </si>
+  <si>
+    <t>TCP dùng số thứ tự để ráp dữ liệu về đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>DNS đổi thứ tự hai gói.</t>
+  </si>
+  <si>
+    <t>Ethernet yêu cầu router gửi lại mọi gói.</t>
+  </si>
+  <si>
+    <t>ICMP tự động ráp dữ liệu ứng dụng.</t>
+  </si>
+  <si>
+    <t>Xét địa chỉ và truyền dữ liệu trong LAN:</t>
+  </si>
+  <si>
+    <t>a) IPv4 được viết theo kiểu dot decimal, các byte ở dạng thập phân và cách nhau bằng dấu chấm.</t>
+  </si>
+  <si>
+    <t>b) MAC được mô tả là địa chỉ 6 byte gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>c) Nếu hai máy cùng LAN, theo bài chỉ cần địa chỉ MAC để máy nhận xác định các gói dành cho mình.</t>
+  </si>
+  <si>
+    <t>d) Nếu hai máy khác LAN, địa chỉ MAC của máy nhận ngoài LAN phải được máy gửi xác định trực tiếp từ đầu thì router mới chuyển được.</t>
+  </si>
+  <si>
+    <t>Xét DNS và ICMP:</t>
+  </si>
+  <si>
+    <t>a) DNS cho phép dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
+  </si>
+  <si>
+    <t>b) Ping dùng ICMP để kiểm tra kết nối giữa các thiết bị.</t>
+  </si>
+  <si>
+    <t>c) Khi người dùng gõ tên miền trong lệnh ping, tên miền có thể thay cho địa chỉ IP theo chức năng DNS được nêu trong bài.</t>
+  </si>
+  <si>
+    <t>d) Vì ping dùng ICMP nên ping có chức năng thay thế TCP trong việc đảm bảo dữ liệu ứng dụng đến đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ IP 131.214.23.16 sang dạng nhị phân.</t>
+  </si>
+  <si>
+    <t>10000011 11010110 00010111 00010000|10000011110101100001011100010000</t>
+  </si>
+  <si>
+    <t>Giao thức được nêu để quy định cách biểu diễn (mã hóa) các trang web là:</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Giao thức cho phép người nhận lấy thư điện tử là:</t>
+  </si>
+  <si>
+    <t>POP3 hoặc IMAP</t>
+  </si>
+  <si>
+    <t>Địa chỉ IP trong bài (IPv4) thường được viết bằng:</t>
+  </si>
+  <si>
+    <t>4 byte ở dạng nhị phân không có dấu phân cách</t>
+  </si>
+  <si>
+    <t>4 byte, mỗi byte viết thập phân và ngăn cách bằng dấu chấm</t>
+  </si>
+  <si>
+    <t>6 byte thập phân</t>
+  </si>
+  <si>
+    <t>8 byte thập phân</t>
+  </si>
+  <si>
+    <t>Vì sao địa chỉ IP có thể khác MAC về tính chất?</t>
+  </si>
+  <si>
+    <t>IP được gán cho thiết bị và có thể thay đổi; MAC gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>IP và MAC luôn giống nhau.</t>
+  </si>
+  <si>
+    <t>IP chỉ dùng trong LAN.</t>
+  </si>
+  <si>
+    <t>MAC dùng để định tuyến Internet.</t>
+  </si>
+  <si>
+    <t>TCP giúp đảm bảo điều gì khi truyền dữ liệu?</t>
+  </si>
+  <si>
+    <t>Dữ liệu đến an toàn, có thể gửi lại khi mất, đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>Chỉ gán địa chỉ IP.</t>
+  </si>
+  <si>
+    <t>Chỉ phân giải tên miền.</t>
+  </si>
+  <si>
+    <t>Chỉ tạo khung Ethernet.</t>
+  </si>
+  <si>
+    <t>DNS có lợi ích chính nào?</t>
+  </si>
+  <si>
+    <t>Dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
+  </si>
+  <si>
+    <t>Thay thế router.</t>
+  </si>
+  <si>
+    <t>Tăng độ dài MAC.</t>
+  </si>
+  <si>
+    <t>Mã hóa SMTP.</t>
+  </si>
+  <si>
+    <t>Đổi 00001010 00011001 00000000 11111111 sang thập phân chọn phương án đúng nhất (câu liên quan vận dụng):</t>
+  </si>
+  <si>
+    <t>10.25.0.255</t>
+  </si>
+  <si>
+    <t>10.25.0.254</t>
+  </si>
+  <si>
+    <t>11.25.0.255</t>
+  </si>
+  <si>
+    <t>10.24.0.255</t>
+  </si>
+  <si>
+    <t>Khi hai máy khác LAN, dữ liệu cần:</t>
+  </si>
+  <si>
+    <t>IP và router chuyển tiếp, rồi MAC trong LAN đích.</t>
+  </si>
+  <si>
+    <t>Chỉ MAC từ đầu đến cuối.</t>
+  </si>
+  <si>
+    <t>Chỉ DNS.</t>
+  </si>
+  <si>
+    <t>Chỉ SMTP.</t>
+  </si>
+  <si>
+    <t>Cơ chế TCP xử lý gói đến lệch thứ tự là:</t>
+  </si>
+  <si>
+    <t>Đánh số gói để ráp lại đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>DNS đổi thứ tự.</t>
+  </si>
+  <si>
+    <t>Ethernet đảo gói.</t>
+  </si>
+  <si>
+    <t>ICMP ráp ứng dụng.</t>
+  </si>
+  <si>
+    <t>Ping gửi loại yêu cầu nào?</t>
+  </si>
+  <si>
+    <t>Router có cổng mặc định khi không có mục đích trong bảng sẽ:</t>
+  </si>
+  <si>
+    <t>Hủy gói.</t>
+  </si>
+  <si>
+    <t>Đổi thành MAC.</t>
+  </si>
+  <si>
+    <t>Gửi DNS.</t>
+  </si>
+  <si>
+    <t>TCP/IP là:</t>
+  </si>
+  <si>
+    <t>Bộ giao thức nền tảng của Internet.</t>
+  </si>
+  <si>
+    <t>Chỉ dùng trong LAN.</t>
+  </si>
+  <si>
+    <t>Chỉ email.</t>
+  </si>
+  <si>
+    <t>Chỉ Ethernet.</t>
+  </si>
+  <si>
+    <t>Xét IP, MAC và LAN:</t>
+  </si>
+  <si>
+    <t>a) IPv4 thường viết 4 byte dạng thập phân cách nhau bằng dấu chấm.</t>
+  </si>
+  <si>
+    <t>b) MAC là địa chỉ gắn với phần cứng.</t>
+  </si>
+  <si>
+    <t>c) Cùng LAN có thể dùng MAC để nhận đúng máy đích.</t>
+  </si>
+  <si>
+    <t>d) Khác LAN thì máy gửi luôn biết sẵn MAC máy nhận từ đầu mà không cần router.</t>
+  </si>
+  <si>
+    <t>Xét TCP:</t>
+  </si>
+  <si>
+    <t>a) TCP kiểm soát truyền dữ liệu.</t>
+  </si>
+  <si>
+    <t>b) TCP có thể yêu cầu gửi lại khi mất gói.</t>
+  </si>
+  <si>
+    <t>c) Đánh số gói giúp ráp đúng thứ tự.</t>
+  </si>
+  <si>
+    <t>d) TCP bảo đảm mọi gói luôn đi cùng một đường và không bao giờ lệch thứ tự.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ 00001010 00011001 00000000 11111111 sang dạng thập phân.</t>
+  </si>
+  <si>
+    <t>Giao thức nào được nêu là giao thức định tuyến/chọn đường?</t>
+  </si>
+  <si>
     <t>IP</t>
   </si>
   <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Transmission Control Protocol</t>
+  </si>
+  <si>
+    <t>Transfer Control Port</t>
+  </si>
+  <si>
+    <t>Transport Connection Protocol</t>
+  </si>
+  <si>
+    <t>Transmission Channel Protocol</t>
+  </si>
+  <si>
+    <t>ICMP được nêu là giao thức cho phép:</t>
+  </si>
+  <si>
+    <t>gửi yêu cầu đến máy tính/thiết bị mạng/ứng dụng để lấy thông tin phản hồi</t>
+  </si>
+  <si>
+    <t>soạn và gửi thư điện tử</t>
+  </si>
+  <si>
+    <t>đổi tên miền thành MAC</t>
+  </si>
+  <si>
+    <t>quy định khung Ethernet</t>
+  </si>
+  <si>
+    <t>Vì sao khi hai máy khác LAN dữ liệu không thể truyền trực tiếp như trong cùng LAN?</t>
+  </si>
+  <si>
+    <t>Máy gửi không thể xác định trực tiếp MAC của máy nhận ngoài LAN và cần router hỗ trợ chuyển tiếp.</t>
+  </si>
+  <si>
+    <t>Vì không có DNS.</t>
+  </si>
+  <si>
+    <t>Vì TCP không hoạt động ngoài LAN.</t>
+  </si>
+  <si>
+    <t>Vì Ethernet không tồn tại trong LAN.</t>
+  </si>
+  <si>
+    <t>Tại sao TCP cần gắn nhãn cổng ứng dụng vào gói dữ liệu?</t>
+  </si>
+  <si>
+    <t>Để dữ liệu không bị lẫn giữa các ứng dụng.</t>
+  </si>
+  <si>
+    <t>Để xác định MAC của router.</t>
+  </si>
+  <si>
+    <t>Để đổi IP thành tên miền.</t>
+  </si>
+  <si>
+    <t>Để xác định địa chỉ đường truyền vật lí.</t>
+  </si>
+  <si>
+    <t>DNS giúp ích gì khi sử dụng Internet?</t>
+  </si>
+  <si>
+    <t>Cho phép dùng tên bằng chữ thay cho địa chỉ IP vốn khó nhớ.</t>
+  </si>
+  <si>
+    <t>Tạo mã kiểm tra Ethernet.</t>
+  </si>
+  <si>
+    <t>Đảm bảo TCP gửi lại mọi gói.</t>
+  </si>
+  <si>
+    <t>Chọn cổng WAN cho router.</t>
+  </si>
+  <si>
+    <t>Một địa chỉ IPv4 có dạng 192.168.13.210. Byte thứ tư ở dạng nhị phân là:</t>
+  </si>
+  <si>
+    <t>11010010</t>
+  </si>
+  <si>
+    <t>11010001</t>
+  </si>
+  <si>
+    <t>10110010</t>
+  </si>
+  <si>
+    <t>11110010</t>
+  </si>
+  <si>
+    <t>Một ứng dụng nhận dữ liệu TCP gồm các gói đến thứ tự 3, 1, 2. Căn cứ bài học, thành phần nào cho phép xác định thứ tự đúng?</t>
+  </si>
+  <si>
+    <t>Số đánh thứ tự các gói TCP.</t>
+  </si>
+  <si>
+    <t>Tên miền DNS.</t>
+  </si>
+  <si>
+    <t>Địa chỉ MAC.</t>
+  </si>
+  <si>
+    <t>Mã kiểm tra Ethernet.</t>
+  </si>
+  <si>
+    <t>Khi Ethernet phát hiện lỗi truyền nhờ mã kiểm tra, theo bài máy nhận có thể:</t>
+  </si>
+  <si>
+    <t>yêu cầu gửi lại dữ liệu.</t>
+  </si>
+  <si>
+    <t>đổi IP thành DNS.</t>
+  </si>
+  <si>
+    <t>chọn cổng WAN.</t>
+  </si>
+  <si>
+    <t>đổi MAC thành TCP.</t>
+  </si>
+  <si>
+    <t>Một học sinh gọi điện thoại qua Internet và nhiều cuộc gọi cùng sử dụng một đường truyền vật lí. Nội dung bài giải thích khả năng này chủ yếu nhờ:</t>
+  </si>
+  <si>
+    <t>dữ liệu được tách thành nhiều gói, cho phép các cuộc truyền xen kẽ trên cùng đường truyền.</t>
+  </si>
+  <si>
+    <t>mỗi cuộc gọi chiếm độc quyền đường truyền.</t>
+  </si>
+  <si>
+    <t>DNS cấp một đường truyền riêng.</t>
+  </si>
+  <si>
+    <t>MAC bị loại bỏ.</t>
+  </si>
+  <si>
+    <t>Một router nhận gói đích không có trong bảng định tuyến. Nếu không có cổng mặc định được cấu hình, theo logic của ví dụ định tuyến tĩnh trong bài, điều kiện cần để router chuyển tiếp theo quy tắc mặc định là:</t>
+  </si>
+  <si>
+    <t>phải có một cổng mặc định.</t>
+  </si>
+  <si>
+    <t>phải có DNS.</t>
+  </si>
+  <si>
+    <t>phải có SMTP.</t>
+  </si>
+  <si>
+    <t>phải có địa chỉ MAC của mọi máy trên Internet.</t>
+  </si>
+  <si>
+    <t>Một máy không ping được thiết bị đích. Chỉ từ thông tin “ping không nhận Echo Reply”, có thể kết luận chắc chắn điều gì theo nội dung bài?</t>
+  </si>
+  <si>
+    <t>Không nhận được phản hồi ICMP Echo Reply từ thiết bị đích.</t>
+  </si>
+  <si>
+    <t>Chắc chắn TCP bị mất gói.</t>
+  </si>
+  <si>
+    <t>Chắc chắn DNS bị lỗi.</t>
+  </si>
+  <si>
+    <t>Chắc chắn Ethernet của mọi router bị lỗi.</t>
+  </si>
+  <si>
+    <t>Xét TCP và ứng dụng:</t>
+  </si>
+  <si>
+    <t>a) TCP cấp cho mỗi ứng dụng một số hiệu gọi là cổng ứng dụng.</t>
+  </si>
+  <si>
+    <t>b) Cổng ứng dụng giúp các gói dữ liệu được gắn nhãn để không lẫn giữa các ứng dụng.</t>
+  </si>
+  <si>
+    <t>c) Nếu hai ứng dụng cùng truyền dữ liệu, việc gắn cổng ứng dụng giúp phân biệt dữ liệu theo ứng dụng.</t>
+  </si>
+  <si>
+    <t>d) Vì có cổng ứng dụng nên TCP không cần đánh số gói và không cần cơ chế xác nhận.</t>
+  </si>
+  <si>
+    <t>Xét Ethernet và truyền gói:</t>
+  </si>
+  <si>
+    <t>a) Ethernet có quy định về khung truyền tín hiệu.</t>
+  </si>
+  <si>
+    <t>b) Việc giới hạn độ dài gói giúp tránh một lượng tin dài không giới hạn gây quá tải máy nhận.</t>
+  </si>
+  <si>
+    <t>c) Khi nhiều cuộc truyền được tách thành các gói, các cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí.</t>
+  </si>
+  <si>
+    <t>d) Việc chia thành gói khiến mỗi cuộc truyền phải độc chiếm đường truyền vật lí trong suốt thời gian truyền.</t>
+  </si>
+  <si>
+    <t>Đổi địa chỉ 192.168.13.210 sang dạng nhị phân.</t>
+  </si>
+  <si>
+    <t>11000000 10101000 00001101 11010010|11000000101010000000110111010010</t>
+  </si>
+  <si>
+    <t>Giao thức nào trong bài quy định cách xử lí khi gửi thư điện tử từ người gửi tới máy chủ thư?</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>Địa chỉ nào được căn cứ khi truyền dữ liệu trong mạng cục bộ theo Ethernet?</t>
+  </si>
+  <si>
     <t>MAC</t>
   </si>
   <si>
@@ -320,549 +863,6 @@
     <t>Cổng ứng dụng</t>
   </si>
   <si>
-    <t>Giao thức kiểm soát việc truyền dữ liệu có tên viết tắt là:</t>
-  </si>
-  <si>
-    <t>Tại sao truyền dữ liệu Ethernet theo từng gói có độ dài xác định?</t>
-  </si>
-  <si>
-    <t>Để tránh một lượng tin dài không giới hạn làm quá tải máy nhận và cản trở các cuộc truyền khác.</t>
-  </si>
-  <si>
-    <t>Để thay thế địa chỉ MAC bằng tên miền.</t>
-  </si>
-  <si>
-    <t>Để router không cần bảng định tuyến.</t>
-  </si>
-  <si>
-    <t>Để mọi dữ liệu chỉ đi qua một đường truyền.</t>
-  </si>
-  <si>
-    <t>Để nơi gửi biết gói tin có sai sót hoặc thất lạc và yêu cầu gửi lại khi cần.</t>
-  </si>
-  <si>
-    <t>Để xác định tên miền cấp cao nhất.</t>
-  </si>
-  <si>
-    <t>Để tạo địa chỉ MAC.</t>
-  </si>
-  <si>
-    <t>Để quy định cách mã hóa trang web.</t>
-  </si>
-  <si>
-    <t>Vì sao nhiều cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí khi dữ liệu được tách thành gói?</t>
-  </si>
-  <si>
-    <t>Vì từng gói của các cuộc truyền có thể được truyền xen kẽ, giúp tận dụng đường truyền.</t>
-  </si>
-  <si>
-    <t>Vì mỗi cuộc truyền được cấp một đường vật lí riêng.</t>
-  </si>
-  <si>
-    <t>Vì router không cần chọn cổng.</t>
-  </si>
-  <si>
-    <t>Vì DNS chia đường truyền thành các tên miền.</t>
-  </si>
-  <si>
-    <t>Một máy có IP 192.168.1.3. Dạng nhị phân tương ứng là:</t>
-  </si>
-  <si>
-    <t>11000000 10101000 00000001 00000011</t>
-  </si>
-  <si>
-    <t>11000000 10101000 00000011 00000001</t>
-  </si>
-  <si>
-    <t>11000000 10101001 00000001 00000011</t>
-  </si>
-  <si>
-    <t>11000000 10101000 00000010 00000011</t>
-  </si>
-  <si>
-    <t>Nhận khung vì IP trùng.</t>
-  </si>
-  <si>
-    <t>Không nhận khung đó vì trong LAN máy tính nhận các gói có MAC đích trùng MAC của mình.</t>
-  </si>
-  <si>
-    <t>Luôn chuyển khung cho DNS.</t>
-  </si>
-  <si>
-    <t>Đổi MAC thành IP rồi nhận.</t>
-  </si>
-  <si>
-    <t>HTTP Request</t>
-  </si>
-  <si>
-    <t>SMTP Request</t>
-  </si>
-  <si>
-    <t>ICMP Echo Request</t>
-  </si>
-  <si>
-    <t>DNS Request</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Một router có nhiều cổng WAN. Gói tin đến có địa chỉ thuộc nhóm được chỉ dẫn đi qua cổng 4. Router nên xử lí thế nào?</t>
-  </si>
-  <si>
-    <t>Chọn cổng 4 để gửi tiếp.</t>
-  </si>
-  <si>
-    <t>Chỉ dùng cổng mặc định dù đã có chỉ dẫn.</t>
-  </si>
-  <si>
-    <t>Gửi qua mọi cổng WAN.</t>
-  </si>
-  <si>
-    <t>Đổi IP thành MAC rồi dừng chuyển tiếp.</t>
-  </si>
-  <si>
-    <t>TCP dùng số thứ tự để ráp dữ liệu về đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>DNS đổi thứ tự hai gói.</t>
-  </si>
-  <si>
-    <t>Ethernet yêu cầu router gửi lại mọi gói.</t>
-  </si>
-  <si>
-    <t>ICMP tự động ráp dữ liệu ứng dụng.</t>
-  </si>
-  <si>
-    <t>Xét địa chỉ và truyền dữ liệu trong LAN:</t>
-  </si>
-  <si>
-    <t>a) IPv4 được viết theo kiểu dot decimal, các byte ở dạng thập phân và cách nhau bằng dấu chấm.</t>
-  </si>
-  <si>
-    <t>b) MAC được mô tả là địa chỉ 6 byte gắn với phần cứng.</t>
-  </si>
-  <si>
-    <t>c) Nếu hai máy cùng LAN, theo bài chỉ cần địa chỉ MAC để máy nhận xác định các gói dành cho mình.</t>
-  </si>
-  <si>
-    <t>d) Nếu hai máy khác LAN, địa chỉ MAC của máy nhận ngoài LAN phải được máy gửi xác định trực tiếp từ đầu thì router mới chuyển được.</t>
-  </si>
-  <si>
-    <t>Xét DNS và ICMP:</t>
-  </si>
-  <si>
-    <t>a) DNS cho phép dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
-  </si>
-  <si>
-    <t>b) Ping dùng ICMP để kiểm tra kết nối giữa các thiết bị.</t>
-  </si>
-  <si>
-    <t>c) Khi người dùng gõ tên miền trong lệnh ping, tên miền có thể thay cho địa chỉ IP theo chức năng DNS được nêu trong bài.</t>
-  </si>
-  <si>
-    <t>d) Vì ping dùng ICMP nên ping có chức năng thay thế TCP trong việc đảm bảo dữ liệu ứng dụng đến đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>Đổi địa chỉ IP 131.214.23.16 sang dạng nhị phân.</t>
-  </si>
-  <si>
-    <t>10000011 11010110 00010111 00010000|10000011110101100001011100010000</t>
-  </si>
-  <si>
-    <t>Giao thức được nêu để quy định cách biểu diễn (mã hóa) các trang web là:</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Giao thức cho phép người nhận lấy thư điện tử là:</t>
-  </si>
-  <si>
-    <t>POP3 hoặc IMAP</t>
-  </si>
-  <si>
-    <t>Địa chỉ IP trong bài (IPv4) thường được viết bằng:</t>
-  </si>
-  <si>
-    <t>4 byte ở dạng nhị phân không có dấu phân cách</t>
-  </si>
-  <si>
-    <t>4 byte, mỗi byte viết thập phân và ngăn cách bằng dấu chấm</t>
-  </si>
-  <si>
-    <t>6 byte thập phân</t>
-  </si>
-  <si>
-    <t>8 byte thập phân</t>
-  </si>
-  <si>
-    <t>Vì sao địa chỉ IP có thể khác MAC về tính chất?</t>
-  </si>
-  <si>
-    <t>IP được gán cho thiết bị và có thể thay đổi; MAC gắn với phần cứng.</t>
-  </si>
-  <si>
-    <t>IP và MAC luôn giống nhau.</t>
-  </si>
-  <si>
-    <t>IP chỉ dùng trong LAN.</t>
-  </si>
-  <si>
-    <t>MAC dùng để định tuyến Internet.</t>
-  </si>
-  <si>
-    <t>TCP giúp đảm bảo điều gì khi truyền dữ liệu?</t>
-  </si>
-  <si>
-    <t>Dữ liệu đến an toàn, có thể gửi lại khi mất, đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>Chỉ gán địa chỉ IP.</t>
-  </si>
-  <si>
-    <t>Chỉ phân giải tên miền.</t>
-  </si>
-  <si>
-    <t>Chỉ tạo khung Ethernet.</t>
-  </si>
-  <si>
-    <t>DNS có lợi ích chính nào?</t>
-  </si>
-  <si>
-    <t>Dùng tên bằng chữ thay cho địa chỉ IP khó nhớ.</t>
-  </si>
-  <si>
-    <t>Thay thế router.</t>
-  </si>
-  <si>
-    <t>Tăng độ dài MAC.</t>
-  </si>
-  <si>
-    <t>Mã hóa SMTP.</t>
-  </si>
-  <si>
-    <t>Đổi 00001010 00011001 00000000 11111111 sang thập phân chọn phương án đúng nhất (câu liên quan vận dụng):</t>
-  </si>
-  <si>
-    <t>10.25.0.255</t>
-  </si>
-  <si>
-    <t>10.25.0.254</t>
-  </si>
-  <si>
-    <t>11.25.0.255</t>
-  </si>
-  <si>
-    <t>10.24.0.255</t>
-  </si>
-  <si>
-    <t>Khi hai máy khác LAN, dữ liệu cần:</t>
-  </si>
-  <si>
-    <t>IP và router chuyển tiếp, rồi MAC trong LAN đích.</t>
-  </si>
-  <si>
-    <t>Chỉ MAC từ đầu đến cuối.</t>
-  </si>
-  <si>
-    <t>Chỉ DNS.</t>
-  </si>
-  <si>
-    <t>Chỉ SMTP.</t>
-  </si>
-  <si>
-    <t>Cơ chế TCP xử lý gói đến lệch thứ tự là:</t>
-  </si>
-  <si>
-    <t>Đánh số gói để ráp lại đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>DNS đổi thứ tự.</t>
-  </si>
-  <si>
-    <t>Ethernet đảo gói.</t>
-  </si>
-  <si>
-    <t>ICMP ráp ứng dụng.</t>
-  </si>
-  <si>
-    <t>Ping gửi loại yêu cầu nào?</t>
-  </si>
-  <si>
-    <t>Router có cổng mặc định khi không có mục đích trong bảng sẽ:</t>
-  </si>
-  <si>
-    <t>Hủy gói.</t>
-  </si>
-  <si>
-    <t>Đổi thành MAC.</t>
-  </si>
-  <si>
-    <t>Gửi DNS.</t>
-  </si>
-  <si>
-    <t>TCP/IP là:</t>
-  </si>
-  <si>
-    <t>Bộ giao thức nền tảng của Internet.</t>
-  </si>
-  <si>
-    <t>Chỉ dùng trong LAN.</t>
-  </si>
-  <si>
-    <t>Chỉ email.</t>
-  </si>
-  <si>
-    <t>Chỉ Ethernet.</t>
-  </si>
-  <si>
-    <t>Xét IP, MAC và LAN:</t>
-  </si>
-  <si>
-    <t>a) IPv4 thường viết 4 byte dạng thập phân cách nhau bằng dấu chấm.</t>
-  </si>
-  <si>
-    <t>b) MAC là địa chỉ gắn với phần cứng.</t>
-  </si>
-  <si>
-    <t>c) Cùng LAN có thể dùng MAC để nhận đúng máy đích.</t>
-  </si>
-  <si>
-    <t>d) Khác LAN thì máy gửi luôn biết sẵn MAC máy nhận từ đầu mà không cần router.</t>
-  </si>
-  <si>
-    <t>Xét TCP:</t>
-  </si>
-  <si>
-    <t>a) TCP kiểm soát truyền dữ liệu.</t>
-  </si>
-  <si>
-    <t>b) TCP có thể yêu cầu gửi lại khi mất gói.</t>
-  </si>
-  <si>
-    <t>c) Đánh số gói giúp ráp đúng thứ tự.</t>
-  </si>
-  <si>
-    <t>d) TCP bảo đảm mọi gói luôn đi cùng một đường và không bao giờ lệch thứ tự.</t>
-  </si>
-  <si>
-    <t>Đổi địa chỉ 00001010 00011001 00000000 11111111 sang dạng thập phân.</t>
-  </si>
-  <si>
-    <t>Giao thức nào được nêu là giao thức định tuyến/chọn đường?</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Transmission Control Protocol</t>
-  </si>
-  <si>
-    <t>Transfer Control Port</t>
-  </si>
-  <si>
-    <t>Transport Connection Protocol</t>
-  </si>
-  <si>
-    <t>Transmission Channel Protocol</t>
-  </si>
-  <si>
-    <t>ICMP được nêu là giao thức cho phép:</t>
-  </si>
-  <si>
-    <t>gửi yêu cầu đến máy tính/thiết bị mạng/ứng dụng để lấy thông tin phản hồi</t>
-  </si>
-  <si>
-    <t>soạn và gửi thư điện tử</t>
-  </si>
-  <si>
-    <t>đổi tên miền thành MAC</t>
-  </si>
-  <si>
-    <t>quy định khung Ethernet</t>
-  </si>
-  <si>
-    <t>Vì sao khi hai máy khác LAN dữ liệu không thể truyền trực tiếp như trong cùng LAN?</t>
-  </si>
-  <si>
-    <t>Máy gửi không thể xác định trực tiếp MAC của máy nhận ngoài LAN và cần router hỗ trợ chuyển tiếp.</t>
-  </si>
-  <si>
-    <t>Vì không có DNS.</t>
-  </si>
-  <si>
-    <t>Vì TCP không hoạt động ngoài LAN.</t>
-  </si>
-  <si>
-    <t>Vì Ethernet không tồn tại trong LAN.</t>
-  </si>
-  <si>
-    <t>Tại sao TCP cần gắn nhãn cổng ứng dụng vào gói dữ liệu?</t>
-  </si>
-  <si>
-    <t>Để dữ liệu không bị lẫn giữa các ứng dụng.</t>
-  </si>
-  <si>
-    <t>Để xác định MAC của router.</t>
-  </si>
-  <si>
-    <t>Để đổi IP thành tên miền.</t>
-  </si>
-  <si>
-    <t>Để xác định địa chỉ đường truyền vật lí.</t>
-  </si>
-  <si>
-    <t>DNS giúp ích gì khi sử dụng Internet?</t>
-  </si>
-  <si>
-    <t>Cho phép dùng tên bằng chữ thay cho địa chỉ IP vốn khó nhớ.</t>
-  </si>
-  <si>
-    <t>Tạo mã kiểm tra Ethernet.</t>
-  </si>
-  <si>
-    <t>Đảm bảo TCP gửi lại mọi gói.</t>
-  </si>
-  <si>
-    <t>Chọn cổng WAN cho router.</t>
-  </si>
-  <si>
-    <t>Một địa chỉ IPv4 có dạng 192.168.13.210. Byte thứ tư ở dạng nhị phân là:</t>
-  </si>
-  <si>
-    <t>11010010</t>
-  </si>
-  <si>
-    <t>11010001</t>
-  </si>
-  <si>
-    <t>10110010</t>
-  </si>
-  <si>
-    <t>11110010</t>
-  </si>
-  <si>
-    <t>Một ứng dụng nhận dữ liệu TCP gồm các gói đến thứ tự 3, 1, 2. Căn cứ bài học, thành phần nào cho phép xác định thứ tự đúng?</t>
-  </si>
-  <si>
-    <t>Số đánh thứ tự các gói TCP.</t>
-  </si>
-  <si>
-    <t>Tên miền DNS.</t>
-  </si>
-  <si>
-    <t>Địa chỉ MAC.</t>
-  </si>
-  <si>
-    <t>Mã kiểm tra Ethernet.</t>
-  </si>
-  <si>
-    <t>Khi Ethernet phát hiện lỗi truyền nhờ mã kiểm tra, theo bài máy nhận có thể:</t>
-  </si>
-  <si>
-    <t>yêu cầu gửi lại dữ liệu.</t>
-  </si>
-  <si>
-    <t>đổi IP thành DNS.</t>
-  </si>
-  <si>
-    <t>chọn cổng WAN.</t>
-  </si>
-  <si>
-    <t>đổi MAC thành TCP.</t>
-  </si>
-  <si>
-    <t>Một học sinh gọi điện thoại qua Internet và nhiều cuộc gọi cùng sử dụng một đường truyền vật lí. Nội dung bài giải thích khả năng này chủ yếu nhờ:</t>
-  </si>
-  <si>
-    <t>dữ liệu được tách thành nhiều gói, cho phép các cuộc truyền xen kẽ trên cùng đường truyền.</t>
-  </si>
-  <si>
-    <t>mỗi cuộc gọi chiếm độc quyền đường truyền.</t>
-  </si>
-  <si>
-    <t>DNS cấp một đường truyền riêng.</t>
-  </si>
-  <si>
-    <t>MAC bị loại bỏ.</t>
-  </si>
-  <si>
-    <t>Một router nhận gói đích không có trong bảng định tuyến. Nếu không có cổng mặc định được cấu hình, theo logic của ví dụ định tuyến tĩnh trong bài, điều kiện cần để router chuyển tiếp theo quy tắc mặc định là:</t>
-  </si>
-  <si>
-    <t>phải có một cổng mặc định.</t>
-  </si>
-  <si>
-    <t>phải có DNS.</t>
-  </si>
-  <si>
-    <t>phải có SMTP.</t>
-  </si>
-  <si>
-    <t>phải có địa chỉ MAC của mọi máy trên Internet.</t>
-  </si>
-  <si>
-    <t>Một máy không ping được thiết bị đích. Chỉ từ thông tin “ping không nhận Echo Reply”, có thể kết luận chắc chắn điều gì theo nội dung bài?</t>
-  </si>
-  <si>
-    <t>Không nhận được phản hồi ICMP Echo Reply từ thiết bị đích.</t>
-  </si>
-  <si>
-    <t>Chắc chắn TCP bị mất gói.</t>
-  </si>
-  <si>
-    <t>Chắc chắn DNS bị lỗi.</t>
-  </si>
-  <si>
-    <t>Chắc chắn Ethernet của mọi router bị lỗi.</t>
-  </si>
-  <si>
-    <t>Xét TCP và ứng dụng:</t>
-  </si>
-  <si>
-    <t>a) TCP cấp cho mỗi ứng dụng một số hiệu gọi là cổng ứng dụng.</t>
-  </si>
-  <si>
-    <t>b) Cổng ứng dụng giúp các gói dữ liệu được gắn nhãn để không lẫn giữa các ứng dụng.</t>
-  </si>
-  <si>
-    <t>c) Nếu hai ứng dụng cùng truyền dữ liệu, việc gắn cổng ứng dụng giúp phân biệt dữ liệu theo ứng dụng.</t>
-  </si>
-  <si>
-    <t>d) Vì có cổng ứng dụng nên TCP không cần đánh số gói và không cần cơ chế xác nhận.</t>
-  </si>
-  <si>
-    <t>Xét Ethernet và truyền gói:</t>
-  </si>
-  <si>
-    <t>a) Ethernet có quy định về khung truyền tín hiệu.</t>
-  </si>
-  <si>
-    <t>b) Việc giới hạn độ dài gói giúp tránh một lượng tin dài không giới hạn gây quá tải máy nhận.</t>
-  </si>
-  <si>
-    <t>c) Khi nhiều cuộc truyền được tách thành các gói, các cuộc truyền có thể xen kẽ trên cùng đường truyền vật lí.</t>
-  </si>
-  <si>
-    <t>d) Việc chia thành gói khiến mỗi cuộc truyền phải độc chiếm đường truyền vật lí trong suốt thời gian truyền.</t>
-  </si>
-  <si>
-    <t>Đổi địa chỉ 192.168.13.210 sang dạng nhị phân.</t>
-  </si>
-  <si>
-    <t>11000000 10101000 00001101 11010010|11000000101010000000110111010010</t>
-  </si>
-  <si>
-    <t>Giao thức nào trong bài quy định cách xử lí khi gửi thư điện tử từ người gửi tới máy chủ thư?</t>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>Địa chỉ nào được căn cứ khi truyền dữ liệu trong mạng cục bộ theo Ethernet?</t>
-  </si>
-  <si>
     <t>Giao thức nào được coi cùng với IP là đặc thù để Internet hoạt động và tạo thành TCP/IP?</t>
   </si>
   <si>
@@ -1016,6 +1016,18 @@
     <t>11000000 10101000 00000001 00000011|11000000101010000000000100000011</t>
   </si>
   <si>
+    <t>Ngày (dd/mm/yyyy)</t>
+  </si>
+  <si>
+    <t>Giờ từ (HH:mm)</t>
+  </si>
+  <si>
+    <t>Giờ đến (HH:mm)</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
     <t>5 MÃ ĐỀ: 101, 202, 303, 404, 505 – Thời gian 15 phút – Ma trận mức độ theo CV 7991</t>
   </si>
   <si>
@@ -1031,6 +1043,15 @@
     <t>Cột I (Mã đề) dùng để hệ thống chọn ngẫu nhiên 1 trong 5 đề cho mỗi học sinh.</t>
   </si>
   <si>
+    <t>Sheet LichThi: mỗi dòng = một suất thi. Cột Từ/Đến dùng định dạng 2026-10-07T07:00 (năm-tháng-ngàyTgiờ:phút).</t>
+  </si>
+  <si>
+    <t>Upload file Excel này lên GitHub data/ → mọi máy tải trang thi sẽ cùng thấy khung giờ.</t>
+  </si>
+  <si>
+    <t>Trên trang GV có nút «Tải lịch .xlsx» để xuất lịch hiện tại.</t>
+  </si>
+  <si>
     <t>NGÔ HOÀNG HẢI ANH</t>
   </si>
   <si>
@@ -1574,108 +1595,43 @@
     <t>Một người dùng biết địa chỉ IP máy chủ nhưng khó nhớ dãy số. Họ muốn sử dụng một tên bằng chữ thay thế địa chỉ IP. Giao thức phù hợp là:</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Cho tên miền </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>example.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>. Theo cách phân lớp tên miền, hãy xác định tên miền cấp cao nhất (TLD)</t>
-    </r>
+    <t>Cho tên miền example.com. Theo cách phân lớp tên miền, hãy xác định tên miền cấp cao nhất (TLD)</t>
   </si>
   <si>
     <t>.com</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Cho tên miền </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>blog.example.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>. Hãy xác định subdomain</t>
-    </r>
+    <t>Giao thức truyền tin trong mạng cục bộ là:</t>
+  </si>
+  <si>
+    <t>Tại sao TCP cần cơ chế xác nhận?</t>
+  </si>
+  <si>
+    <t>Một thiết bị nhận dữ liệu trong LAN nhưng địa chỉ MAC đích của khung không trùng với MAC của thiết bị đó. Theo mô tả thiết bị đó:</t>
+  </si>
+  <si>
+    <t>Khi ping một thiết bị, công cụ ping gửi loại yêu cầu nào?</t>
+  </si>
+  <si>
+    <t>Một học sinh nhập ping www.google.com. Tên miền trong lệnh ping có thể được dùng thay cho địa chỉ IP nhờ cơ chế của:</t>
+  </si>
+  <si>
+    <t>Hai gói dữ liệu của cùng một ứng dụng đi theo các đường khác nhau và gói B đến trước gói A. Xử lí nào phù hợp nhất?</t>
+  </si>
+  <si>
+    <t>Cho tên miền blog.example.com. Hãy xác định subdomain</t>
   </si>
   <si>
     <t>blog</t>
   </si>
   <si>
-    <t>Giao thức truyền tin trong mạng cục bộ là:</t>
-  </si>
-  <si>
-    <t>Tại sao TCP cần cơ chế xác nhận?</t>
-  </si>
-  <si>
-    <t>Một thiết bị nhận dữ liệu trong LAN nhưng địa chỉ MAC đích của khung không trùng với MAC của thiết bị đó. Theo mô tả thiết bị đó:</t>
-  </si>
-  <si>
-    <t>Khi ping một thiết bị, công cụ ping gửi loại yêu cầu nào?</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Một học sinh nhập ping </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>www.google.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>. Tên miền trong lệnh ping có thể được dùng thay cho địa chỉ IP nhờ cơ chế của:</t>
-    </r>
-  </si>
-  <si>
-    <t>Hai gói dữ liệu của cùng một ứng dụng đi theo các đường khác nhau và gói B đến trước gói A. Xử lí nào phù hợp nhất?</t>
+    <t>Một người dùng muốn gửi một email đến người khác. Trong ba giao thức SMTP, POP3, IMAP, giao thức nào được sử dụng cho hoạt động gửi email?</t>
   </si>
   <si>
     <t>Tên đầy đủ của TCP là:</t>
   </si>
   <si>
-    <t>Một người dùng muốn gửi một email đến người khác. Trong ba giao thức SMTP, POP3, IMAP, giao thức nào được sử dụng cho hoạt động gửi email?</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Một hệ thống thư điện tử cần thực hiện hai chức năng: gửi thư từ người gửi đến máy chủ thư và nhận thư từ máy chủ về cho người dùng. Hãy xác định giao thức phù hợp cho chức năng </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Nhận thư</t>
-    </r>
+    <t>Một hệ thống thư điện tử cần thực hiện hai chức năng: gửi thư từ người gửi đến máy chủ thư và nhận thư từ máy chủ về cho người dùng. Hãy xác định giao thức phù hợp cho chức năng Nhận thư</t>
   </si>
   <si>
     <t>Một gói TCP bị thất lạc trên đường truyền. Điều gì giúp nơi gửi biết để yêu cầu truyền lại?</t>
@@ -1684,78 +1640,20 @@
     <t>Một người nhận thư muốn tải thư từ hộp thư về. Trong các giao thức, lựa chọn phù hợp là:</t>
   </si>
   <si>
-    <r>
-      <t>Một người dùng muốn kiểm tra kết nối đến “</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>www.google.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>” bằng lệnh ping. Chuỗi chức năng phù hợp là:</t>
-    </r>
+    <t>Một người dùng muốn kiểm tra kết nối đến “www.google.com” bằng lệnh ping. Chuỗi chức năng phù hợp là:</t>
   </si>
   <si>
     <t>Một router đã đưa gói tin tới LAN đích. Để gói tới đúng máy nhận trong LAN, theo bạn cần dựa vào:</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Cho tên miền </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>www.example.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Giao thức nào có chức năng chuyển đổi tên miền dễ nhớ thành địa chỉ IP để máy tính có thể xác định máy chủ cần truy cập?</t>
-    </r>
-  </si>
-  <si>
-    <t>Từ</t>
-  </si>
-  <si>
-    <t>Đến</t>
-  </si>
-  <si>
-    <t>2026-10-05T08:00</t>
-  </si>
-  <si>
-    <t>2026-10-05T17:00</t>
-  </si>
-  <si>
-    <t>Sheet LichThi: mỗi dòng = một suất thi. Cột Từ/Đến dùng định dạng 2026-10-07T07:00 (năm-tháng-ngàyTgiờ:phút).</t>
-  </si>
-  <si>
-    <t>Upload file Excel này lên GitHub data/ → mọi máy tải trang thi sẽ cùng thấy khung giờ.</t>
-  </si>
-  <si>
-    <t>Trên trang GV có nút «Tải lịch .xlsx» để xuất lịch hiện tại.</t>
+    <t>Cho tên miền www.example.com. Giao thức nào có chức năng chuyển đổi tên miền dễ nhớ thành địa chỉ IP để máy tính có thể xác định máy chủ cần truy cập?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1780,15 +1678,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1836,7 +1729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1847,13 +1740,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2157,14 +2058,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C179"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2175,1468 +2076,1468 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>6</v>
       </c>
       <c r="B160" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
       <c r="B161" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -3647,7 +3548,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
@@ -3656,7 +3557,7 @@
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -3685,7 +3586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3714,7 +3615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -3743,7 +3644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -3772,7 +3673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -3801,7 +3702,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -3830,7 +3731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -3859,7 +3760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -3867,7 +3768,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>50</v>
@@ -3888,7 +3789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1</v>
       </c>
@@ -3917,7 +3818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1</v>
       </c>
@@ -3925,7 +3826,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>59</v>
@@ -3946,7 +3847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -3975,7 +3876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>1</v>
       </c>
@@ -4004,7 +3905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -4012,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4033,7 +3934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -4062,7 +3963,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>2</v>
       </c>
@@ -4091,7 +3992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -4112,36 +4013,36 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>516</v>
+      <c r="C17" s="4" t="s">
+        <v>523</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="6" t="s">
-        <v>517</v>
+      <c r="H17" s="4" t="s">
+        <v>524</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>1</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>520</v>
+      <c r="C18" s="4" t="s">
+        <v>525</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>74</v>
@@ -4162,7 +4063,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -4173,16 +4074,16 @@
         <v>93</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>95</v>
+        <v>276</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>97</v>
+        <v>278</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>29</v>
@@ -4191,7 +4092,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>1</v>
       </c>
@@ -4199,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>73</v>
@@ -4220,7 +4121,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>1</v>
       </c>
@@ -4228,19 +4129,19 @@
         <v>16</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>22</v>
@@ -4249,27 +4150,27 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>1</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>521</v>
+      <c r="C22" s="4" t="s">
+        <v>526</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>22</v>
@@ -4278,7 +4179,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>1</v>
       </c>
@@ -4286,19 +4187,19 @@
         <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>22</v>
@@ -4307,7 +4208,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>1</v>
       </c>
@@ -4315,19 +4216,19 @@
         <v>16</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>22</v>
@@ -4336,27 +4237,27 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>1</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>522</v>
+      <c r="C25" s="4" t="s">
+        <v>527</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>29</v>
@@ -4365,44 +4266,44 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>1</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>523</v>
+      <c r="C26" s="4" t="s">
+        <v>528</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>1</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>524</v>
+      <c r="C27" s="4" t="s">
+        <v>529</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>28</v>
@@ -4423,7 +4324,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>1</v>
       </c>
@@ -4431,19 +4332,19 @@
         <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>22</v>
@@ -4452,27 +4353,27 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>1</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>525</v>
+      <c r="C29" s="4" t="s">
+        <v>530</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>22</v>
@@ -4481,7 +4382,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>2</v>
       </c>
@@ -4489,19 +4390,19 @@
         <v>76</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>82</v>
@@ -4510,7 +4411,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>2</v>
       </c>
@@ -4518,19 +4419,19 @@
         <v>76</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>82</v>
@@ -4539,7 +4440,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>3</v>
       </c>
@@ -4547,41 +4448,41 @@
         <v>88</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>3</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>518</v>
+      <c r="C33" s="4" t="s">
+        <v>531</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="6" t="s">
-        <v>519</v>
+      <c r="H33" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>1</v>
       </c>
@@ -4589,7 +4490,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>91</v>
@@ -4607,10 +4508,10 @@
         <v>22</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>1</v>
       </c>
@@ -4618,10 +4519,10 @@
         <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>26</v>
@@ -4636,10 +4537,10 @@
         <v>22</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>1</v>
       </c>
@@ -4647,28 +4548,28 @@
         <v>16</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>1</v>
       </c>
@@ -4676,28 +4577,28 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>1</v>
       </c>
@@ -4705,28 +4606,28 @@
         <v>16</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>1</v>
       </c>
@@ -4734,28 +4635,28 @@
         <v>16</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>1</v>
       </c>
@@ -4763,28 +4664,28 @@
         <v>16</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>1</v>
       </c>
@@ -4792,28 +4693,28 @@
         <v>16</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>1</v>
       </c>
@@ -4821,28 +4722,28 @@
         <v>16</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>1</v>
       </c>
@@ -4850,28 +4751,28 @@
         <v>16</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="I43" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>1</v>
       </c>
@@ -4879,28 +4780,28 @@
         <v>16</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>70</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>1</v>
       </c>
@@ -4908,28 +4809,28 @@
         <v>16</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2</v>
       </c>
@@ -4937,28 +4838,28 @@
         <v>76</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>2</v>
       </c>
@@ -4966,28 +4867,28 @@
         <v>76</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>3</v>
       </c>
@@ -4995,41 +4896,41 @@
         <v>88</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>3</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>527</v>
+      <c r="C49" s="4" t="s">
+        <v>533</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="6" t="s">
+      <c r="H49" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>1</v>
       </c>
@@ -5037,10 +4938,10 @@
         <v>16</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>26</v>
@@ -5055,39 +4956,39 @@
         <v>22</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>1</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>526</v>
+      <c r="C51" s="4" t="s">
+        <v>534</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>1</v>
       </c>
@@ -5095,28 +4996,28 @@
         <v>16</v>
       </c>
       <c r="C52" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>1</v>
       </c>
@@ -5124,28 +5025,28 @@
         <v>16</v>
       </c>
       <c r="C53" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>1</v>
       </c>
@@ -5153,28 +5054,28 @@
         <v>16</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>1</v>
       </c>
@@ -5182,28 +5083,28 @@
         <v>16</v>
       </c>
       <c r="C55" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>1</v>
       </c>
@@ -5211,28 +5112,28 @@
         <v>16</v>
       </c>
       <c r="C56" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>1</v>
       </c>
@@ -5240,28 +5141,28 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="G57" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>1</v>
       </c>
@@ -5269,28 +5170,28 @@
         <v>16</v>
       </c>
       <c r="C58" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>1</v>
       </c>
@@ -5298,28 +5199,28 @@
         <v>16</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>1</v>
       </c>
@@ -5327,28 +5228,28 @@
         <v>16</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>1</v>
       </c>
@@ -5356,28 +5257,28 @@
         <v>16</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>2</v>
       </c>
@@ -5385,28 +5286,28 @@
         <v>76</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>2</v>
       </c>
@@ -5414,28 +5315,28 @@
         <v>76</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>3</v>
       </c>
@@ -5443,41 +5344,41 @@
         <v>88</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="38" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>3</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>528</v>
+      <c r="C65" s="4" t="s">
+        <v>535</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="6" t="s">
-        <v>151</v>
+      <c r="H65" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>1</v>
       </c>
@@ -5485,7 +5386,7 @@
         <v>16</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>26</v>
@@ -5503,10 +5404,10 @@
         <v>22</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>1</v>
       </c>
@@ -5514,28 +5415,28 @@
         <v>16</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>1</v>
       </c>
@@ -5561,10 +5462,10 @@
         <v>22</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>1</v>
       </c>
@@ -5590,10 +5491,10 @@
         <v>22</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>1</v>
       </c>
@@ -5619,10 +5520,10 @@
         <v>22</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>1</v>
       </c>
@@ -5648,10 +5549,10 @@
         <v>22</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>1</v>
       </c>
@@ -5677,10 +5578,10 @@
         <v>22</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>1</v>
       </c>
@@ -5706,27 +5607,27 @@
         <v>22</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>1</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>529</v>
+      <c r="C74" s="4" t="s">
+        <v>536</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>305</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>306</v>
@@ -5735,18 +5636,18 @@
         <v>22</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>1</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>530</v>
+      <c r="C75" s="4" t="s">
+        <v>537</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>307</v>
@@ -5764,18 +5665,18 @@
         <v>22</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>1</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>531</v>
+      <c r="C76" s="4" t="s">
+        <v>538</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>311</v>
@@ -5793,18 +5694,18 @@
         <v>22</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>1</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>532</v>
+      <c r="C77" s="4" t="s">
+        <v>539</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>315</v>
@@ -5822,10 +5723,10 @@
         <v>22</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>2</v>
       </c>
@@ -5851,10 +5752,10 @@
         <v>82</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>2</v>
       </c>
@@ -5880,10 +5781,10 @@
         <v>82</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>3</v>
       </c>
@@ -5901,28 +5802,28 @@
         <v>329</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="38" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>3</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>533</v>
+      <c r="C81" s="4" t="s">
+        <v>540</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="7" t="s">
+      <c r="H81" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -5932,35 +5833,121 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46213</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.28125</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46213</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.47222222222222221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.28125</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.3125</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -5968,73 +5955,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672EBABE-4377-4EE0-99D1-ED1DD8A96285}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
-  </cols>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>537</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D65FB64-43B5-4101-A4E1-D57ABE446BD8}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>